--- a/output/model_analysis_20260429/model_bin_risk_performance_pivot.xlsx
+++ b/output/model_analysis_20260429/model_bin_risk_performance_pivot.xlsx
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,13 +37,22 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="00333333"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -52,7 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F6F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -87,41 +101,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="10" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1318,7 +1346,7 @@
       <c r="F6" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="7" t="n">
         <v>86</v>
       </c>
     </row>
@@ -1462,7 +1490,7 @@
       <c r="F14" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1606,7 +1634,7 @@
       <c r="F22" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G22" s="7" t="n">
         <v>81</v>
       </c>
     </row>
@@ -1662,22 +1690,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="8" t="n">
+      <c r="B27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1687,22 +1715,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="7" t="n">
+      <c r="B28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="F28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="8" t="n">
+      <c r="F28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="9" t="n">
         <v>0.05714285714285714</v>
       </c>
     </row>
@@ -1712,20 +1740,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="7" t="n">
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="G29" s="8" t="n">
+      <c r="G29" s="9" t="n">
         <v>0.1363636363636364</v>
       </c>
     </row>
@@ -1735,22 +1763,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="8" t="n">
+      <c r="B30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9" t="n">
         <v>0.1052631578947368</v>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="F30" s="9" t="n">
         <v>0.1764705882352941</v>
       </c>
-      <c r="G30" s="8" t="n">
+      <c r="G30" s="10" t="n">
         <v>0.05813953488372093</v>
       </c>
     </row>
@@ -1894,7 +1922,7 @@
       <c r="F38" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="G38" s="7" t="n">
         <v>98</v>
       </c>
     </row>
@@ -2038,7 +2066,7 @@
       <c r="F46" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G46" s="5" t="n">
+      <c r="G46" s="7" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2182,7 +2210,7 @@
       <c r="F54" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="G54" s="5" t="n">
+      <c r="G54" s="7" t="n">
         <v>94</v>
       </c>
     </row>
@@ -2238,22 +2266,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="8" t="n">
+      <c r="B59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2263,22 +2291,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="7" t="n">
+      <c r="B60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="8" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="F60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="8" t="n">
+      <c r="F60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="9" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -2288,20 +2316,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B61" s="7" t="n"/>
-      <c r="C61" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="7" t="n">
+      <c r="B61" s="8" t="n"/>
+      <c r="C61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="8" t="n">
         <v>0.125</v>
       </c>
-      <c r="F61" s="7" t="n">
+      <c r="F61" s="8" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="G61" s="8" t="n">
+      <c r="G61" s="9" t="n">
         <v>0.1304347826086956</v>
       </c>
     </row>
@@ -2311,22 +2339,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B62" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="8" t="n">
+      <c r="B62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="9" t="n">
         <v>0.09523809523809523</v>
       </c>
-      <c r="F62" s="8" t="n">
+      <c r="F62" s="9" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="G62" s="8" t="n">
+      <c r="G62" s="10" t="n">
         <v>0.04081632653061224</v>
       </c>
     </row>
@@ -2403,22 +2431,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="10" t="n">
+      <c r="B3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2428,22 +2456,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="9" t="n">
+      <c r="B4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11" t="n">
         <v>2945.06</v>
       </c>
-      <c r="F4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="10" t="n">
+      <c r="F4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="12" t="n">
         <v>2945.06</v>
       </c>
     </row>
@@ -2453,20 +2481,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n"/>
-      <c r="C5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="9" t="n">
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11" t="n">
         <v>1495.57</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="12" t="n">
         <v>1495.57</v>
       </c>
     </row>
@@ -2476,22 +2504,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="10" t="n">
+      <c r="B6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="12" t="n">
         <v>2945.06</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="12" t="n">
         <v>1495.57</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="13" t="n">
         <v>4440.63</v>
       </c>
     </row>
@@ -2547,22 +2575,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="11" t="n">
         <v>17650</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="11" t="n">
         <v>15575</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="11" t="n">
         <v>2650</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="11" t="n">
         <v>1025</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="11" t="n">
         <v>1725</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="12" t="n">
         <v>38625</v>
       </c>
     </row>
@@ -2572,22 +2600,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="11" t="n">
         <v>3400</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="11" t="n">
         <v>10025</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="11" t="n">
         <v>6450</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="11" t="n">
         <v>13625</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="11" t="n">
         <v>4225</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="12" t="n">
         <v>37725</v>
       </c>
     </row>
@@ -2597,20 +2625,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n">
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="11" t="n">
         <v>2200</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="11" t="n">
         <v>7125</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="11" t="n">
         <v>7925</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G13" s="12" t="n">
         <v>17750</v>
       </c>
     </row>
@@ -2620,22 +2648,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
+      <c r="B14" s="12" t="n">
         <v>21050</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="12" t="n">
         <v>26100</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="12" t="n">
         <v>11300</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="12" t="n">
         <v>21775</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="12" t="n">
         <v>13875</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="G14" s="13" t="n">
         <v>94100</v>
       </c>
     </row>
@@ -2691,22 +2719,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="8" t="n">
+      <c r="B19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2716,22 +2744,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="7" t="n">
+      <c r="B20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="8" t="n">
         <v>0.2161511926605505</v>
       </c>
-      <c r="F20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="8" t="n">
+      <c r="F20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="9" t="n">
         <v>0.07806653412856196</v>
       </c>
     </row>
@@ -2741,20 +2769,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="7" t="n">
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8" t="n">
         <v>0.1887154574132492</v>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="G21" s="9" t="n">
         <v>0.08425746478873239</v>
       </c>
     </row>
@@ -2764,22 +2792,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="8" t="n">
+      <c r="B22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9" t="n">
         <v>0.135249598163031</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="9" t="n">
         <v>0.1077888288288288</v>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="G22" s="10" t="n">
         <v>0.04719054197662062</v>
       </c>
     </row>
@@ -2835,22 +2863,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n">
+      <c r="B27" s="11" t="n">
         <v>1068.43</v>
       </c>
-      <c r="C27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="10" t="n">
+      <c r="C27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="12" t="n">
         <v>1068.43</v>
       </c>
     </row>
@@ -2860,22 +2888,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="9" t="n">
+      <c r="B28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="11" t="n">
         <v>2647.62</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="11" t="n">
         <v>352.94</v>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="G28" s="12" t="n">
         <v>3000.56</v>
       </c>
     </row>
@@ -2885,20 +2913,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="9" t="n">
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="11" t="n">
         <v>2122.93</v>
       </c>
-      <c r="G29" s="10" t="n">
+      <c r="G29" s="12" t="n">
         <v>2122.93</v>
       </c>
     </row>
@@ -2908,22 +2936,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n">
+      <c r="B30" s="12" t="n">
         <v>1068.43</v>
       </c>
-      <c r="C30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="10" t="n">
+      <c r="C30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="12" t="n">
         <v>2647.62</v>
       </c>
-      <c r="F30" s="10" t="n">
+      <c r="F30" s="12" t="n">
         <v>2475.87</v>
       </c>
-      <c r="G30" s="10" t="n">
+      <c r="G30" s="13" t="n">
         <v>6191.92</v>
       </c>
     </row>
@@ -2979,22 +3007,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n">
+      <c r="B35" s="11" t="n">
         <v>17650</v>
       </c>
-      <c r="C35" s="9" t="n">
+      <c r="C35" s="11" t="n">
         <v>15575</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="11" t="n">
         <v>2650</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="11" t="n">
         <v>1025</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="11" t="n">
         <v>1725</v>
       </c>
-      <c r="G35" s="10" t="n">
+      <c r="G35" s="12" t="n">
         <v>38625</v>
       </c>
     </row>
@@ -3004,22 +3032,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n">
+      <c r="B36" s="11" t="n">
         <v>3400</v>
       </c>
-      <c r="C36" s="9" t="n">
+      <c r="C36" s="11" t="n">
         <v>10025</v>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" s="11" t="n">
         <v>6450</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="11" t="n">
         <v>13625</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="11" t="n">
         <v>4225</v>
       </c>
-      <c r="G36" s="10" t="n">
+      <c r="G36" s="12" t="n">
         <v>37725</v>
       </c>
     </row>
@@ -3029,20 +3057,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n">
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="11" t="n">
         <v>2200</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" s="11" t="n">
         <v>7125</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="11" t="n">
         <v>7925</v>
       </c>
-      <c r="G37" s="10" t="n">
+      <c r="G37" s="12" t="n">
         <v>17750</v>
       </c>
     </row>
@@ -3052,22 +3080,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B38" s="10" t="n">
+      <c r="B38" s="12" t="n">
         <v>21050</v>
       </c>
-      <c r="C38" s="10" t="n">
+      <c r="C38" s="12" t="n">
         <v>26100</v>
       </c>
-      <c r="D38" s="10" t="n">
+      <c r="D38" s="12" t="n">
         <v>11300</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="12" t="n">
         <v>21775</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="12" t="n">
         <v>13875</v>
       </c>
-      <c r="G38" s="10" t="n">
+      <c r="G38" s="13" t="n">
         <v>94100</v>
       </c>
     </row>
@@ -3123,22 +3151,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B43" s="7" t="n">
+      <c r="B43" s="8" t="n">
         <v>0.06053427762039661</v>
       </c>
-      <c r="C43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="8" t="n">
+      <c r="C43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="9" t="n">
         <v>0.02766161812297735</v>
       </c>
     </row>
@@ -3148,22 +3176,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="7" t="n">
+      <c r="B44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="8" t="n">
         <v>0.1943207339449541</v>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F44" s="8" t="n">
         <v>0.08353609467455621</v>
       </c>
-      <c r="G44" s="8" t="n">
+      <c r="G44" s="9" t="n">
         <v>0.0795377070907886</v>
       </c>
     </row>
@@ -3173,20 +3201,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B45" s="7" t="n"/>
-      <c r="C45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="7" t="n">
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="8" t="n">
         <v>0.2678776025236593</v>
       </c>
-      <c r="G45" s="8" t="n">
+      <c r="G45" s="9" t="n">
         <v>0.1196016901408451</v>
       </c>
     </row>
@@ -3196,22 +3224,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B46" s="8" t="n">
+      <c r="B46" s="9" t="n">
         <v>0.05075676959619953</v>
       </c>
-      <c r="C46" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="8" t="n">
+      <c r="C46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="9" t="n">
         <v>0.1215898966704937</v>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F46" s="9" t="n">
         <v>0.1784410810810811</v>
       </c>
-      <c r="G46" s="8" t="n">
+      <c r="G46" s="10" t="n">
         <v>0.06580148777895856</v>
       </c>
     </row>
@@ -3288,22 +3316,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n">
+      <c r="B3" s="14" t="n">
         <v>0.0577928865222811</v>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="14" t="n">
         <v>0.06610009615858989</v>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="14" t="n">
         <v>0.06689377519236493</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" s="14" t="n">
         <v>0.0362809958464943</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" s="14" t="n">
         <v>0.0883014953417364</v>
       </c>
-      <c r="G3" s="12" t="n">
+      <c r="G3" s="15" t="n">
         <v>0.06203178427401005</v>
       </c>
     </row>
@@ -3313,22 +3341,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="14" t="n">
         <v>0.06126832174503703</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="14" t="n">
         <v>0.06177054996739424</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="14" t="n">
         <v>0.0563004874639454</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="14" t="n">
         <v>0.06337038055148971</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="14" t="n">
         <v>0.04846571286640807</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="15" t="n">
         <v>0.05924728981713567</v>
       </c>
     </row>
@@ -3338,20 +3366,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n">
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n">
         <v>0.0303980241284316</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="14" t="n">
         <v>0.07126428996341931</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="14" t="n">
         <v>0.05258242726948031</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="14" t="n">
         <v>0.05840024437431996</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="15" t="n">
         <v>0.05683708696921964</v>
       </c>
     </row>
@@ -3361,22 +3389,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="15" t="n">
         <v>0.0584548741837584</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="15" t="n">
         <v>0.06289520846115487</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="15" t="n">
         <v>0.0621982775165362</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="15" t="n">
         <v>0.05797071336286728</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="15" t="n">
         <v>0.05674991448098357</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="16" t="n">
         <v>0.05969988713981658</v>
       </c>
     </row>
@@ -3432,22 +3460,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="11" t="n">
         <v>2580.882352941177</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="11" t="n">
         <v>1901.785714285714</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="11" t="n">
         <v>3333.333333333333</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="11" t="n">
         <v>5000</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="11" t="n">
         <v>2800</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="12" t="n">
         <v>2452.777777777778</v>
       </c>
     </row>
@@ -3457,22 +3485,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="11" t="n">
         <v>1875</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="11" t="n">
         <v>1988.636363636364</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="11" t="n">
         <v>2717.857142857143</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="11" t="n">
         <v>2537.5</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="11" t="n">
         <v>1433.333333333333</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="12" t="n">
         <v>2186.25</v>
       </c>
     </row>
@@ -3482,20 +3510,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n">
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n">
         <v>2050</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="11" t="n">
         <v>1000</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="11" t="n">
         <v>2775</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="11" t="n">
         <v>1586.363636363636</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G13" s="12" t="n">
         <v>1943.478260869565</v>
       </c>
     </row>
@@ -3505,22 +3533,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
+      <c r="B14" s="12" t="n">
         <v>2446.428571428572</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="12" t="n">
         <v>1944.230769230769</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="12" t="n">
         <v>2463.461538461539</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="12" t="n">
         <v>2745.238095238095</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="12" t="n">
         <v>1602.777777777778</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="G14" s="13" t="n">
         <v>2226.767676767677</v>
       </c>
     </row>
@@ -3576,22 +3604,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B19" s="11" t="n">
         <v>1361.764705882353</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="11" t="n">
         <v>1148.214285714286</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="11" t="n">
         <v>883.3333333333334</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="11" t="n">
         <v>1025</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="11" t="n">
         <v>1725</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="G19" s="12" t="n">
         <v>1239.583333333333</v>
       </c>
     </row>
@@ -3601,22 +3629,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="11" t="n">
         <v>850</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="11" t="n">
         <v>911.3636363636364</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="11" t="n">
         <v>921.4285714285714</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="11" t="n">
         <v>1135.416666666667</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="11" t="n">
         <v>704.1666666666666</v>
       </c>
-      <c r="G20" s="10" t="n">
+      <c r="G20" s="12" t="n">
         <v>943.125</v>
       </c>
     </row>
@@ -3626,20 +3654,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n">
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" s="11" t="n">
         <v>733.3333333333334</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="11" t="n">
         <v>890.625</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="11" t="n">
         <v>720.4545454545455</v>
       </c>
-      <c r="G21" s="10" t="n">
+      <c r="G21" s="12" t="n">
         <v>771.7391304347826</v>
       </c>
     </row>
@@ -3649,22 +3677,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B22" s="12" t="n">
         <v>1264.285714285714</v>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C22" s="12" t="n">
         <v>1023.076923076923</v>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="12" t="n">
         <v>869.2307692307693</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="12" t="n">
         <v>1036.904761904762</v>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="12" t="n">
         <v>770.8333333333334</v>
       </c>
-      <c r="G22" s="10" t="n">
+      <c r="G22" s="13" t="n">
         <v>1011.111111111111</v>
       </c>
     </row>
@@ -3720,22 +3748,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n">
+      <c r="B27" s="11" t="n">
         <v>2365.427745098039</v>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="11" t="n">
         <v>1701.684523809524</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="11" t="n">
         <v>1263.166666666667</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="11" t="n">
         <v>3401.775</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="11" t="n">
         <v>6621.896666666667</v>
       </c>
-      <c r="G27" s="10" t="n">
+      <c r="G27" s="12" t="n">
         <v>2162.472962962963</v>
       </c>
     </row>
@@ -3745,22 +3773,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B28" s="11" t="n">
         <v>1813.700416666666</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="11" t="n">
         <v>1019.511212121212</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="11" t="n">
         <v>2609.839761904761</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="11" t="n">
         <v>1927.416111111111</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="11" t="n">
         <v>1710.215</v>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="G28" s="12" t="n">
         <v>1753.214666666667</v>
       </c>
     </row>
@@ -3770,20 +3798,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n">
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n">
         <v>1990.17</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="11" t="n">
         <v>1002.82</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="11" t="n">
         <v>2654.001458333333</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="11" t="n">
         <v>1592.921515151515</v>
       </c>
-      <c r="G29" s="10" t="n">
+      <c r="G29" s="12" t="n">
         <v>1902.294710144928</v>
       </c>
     </row>
@@ -3793,22 +3821,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n">
+      <c r="B30" s="12" t="n">
         <v>2260.336825396825</v>
       </c>
-      <c r="C30" s="10" t="n">
+      <c r="C30" s="12" t="n">
         <v>1424.168333333333</v>
       </c>
-      <c r="D30" s="10" t="n">
+      <c r="D30" s="12" t="n">
         <v>1928.218333333333</v>
       </c>
-      <c r="E30" s="10" t="n">
+      <c r="E30" s="12" t="n">
         <v>2274.418095238095</v>
       </c>
-      <c r="F30" s="10" t="n">
+      <c r="F30" s="12" t="n">
         <v>1911.406851851852</v>
       </c>
-      <c r="G30" s="10" t="n">
+      <c r="G30" s="13" t="n">
         <v>1936.670622895623</v>
       </c>
     </row>
@@ -3864,22 +3892,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n">
+      <c r="B35" s="11" t="n">
         <v>1910.793529411765</v>
       </c>
-      <c r="C35" s="9" t="n">
+      <c r="C35" s="11" t="n">
         <v>1284.228214285714</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="11" t="n">
         <v>891.9227777777779</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="11" t="n">
         <v>3148.925</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="11" t="n">
         <v>5839.903333333333</v>
       </c>
-      <c r="G35" s="10" t="n">
+      <c r="G35" s="12" t="n">
         <v>1725.757824074074</v>
       </c>
     </row>
@@ -3889,22 +3917,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n">
+      <c r="B36" s="11" t="n">
         <v>1421.17625</v>
       </c>
-      <c r="C36" s="9" t="n">
+      <c r="C36" s="11" t="n">
         <v>717.9643939393939</v>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" s="11" t="n">
         <v>2331.138333333333</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="11" t="n">
         <v>1505.116527777777</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="11" t="n">
         <v>1415.172777777778</v>
       </c>
-      <c r="G36" s="10" t="n">
+      <c r="G36" s="12" t="n">
         <v>1411.317916666666</v>
       </c>
     </row>
@@ -3914,20 +3942,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n">
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n">
         <v>1712.836666666667</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="11" t="n">
         <v>721.4566666666666</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" s="11" t="n">
         <v>2348.330833333333</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="11" t="n">
         <v>1322.805151515151</v>
       </c>
-      <c r="G37" s="10" t="n">
+      <c r="G37" s="12" t="n">
         <v>1618.030869565217</v>
       </c>
     </row>
@@ -3937,22 +3965,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B38" s="10" t="n">
+      <c r="B38" s="12" t="n">
         <v>1817.533095238095</v>
       </c>
-      <c r="C38" s="10" t="n">
+      <c r="C38" s="12" t="n">
         <v>1061.14</v>
       </c>
-      <c r="D38" s="10" t="n">
+      <c r="D38" s="12" t="n">
         <v>1627.546666666666</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="12" t="n">
         <v>1904.617619047619</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="12" t="n">
         <v>1604.544259259259</v>
       </c>
-      <c r="G38" s="10" t="n">
+      <c r="G38" s="13" t="n">
         <v>1573.683922558922</v>
       </c>
     </row>
@@ -4008,22 +4036,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n">
+      <c r="B43" s="11" t="n">
         <v>8369.528725490196</v>
       </c>
-      <c r="C43" s="9" t="n">
+      <c r="C43" s="11" t="n">
         <v>6349.381071428571</v>
       </c>
-      <c r="D43" s="9" t="n">
+      <c r="D43" s="11" t="n">
         <v>5616.231111111109</v>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="11" t="n">
         <v>6969.213333333333</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="11" t="n">
         <v>8855.946666666665</v>
       </c>
-      <c r="G43" s="10" t="n">
+      <c r="G43" s="12" t="n">
         <v>7329.088240740742</v>
       </c>
     </row>
@@ -4033,22 +4061,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n">
+      <c r="B44" s="11" t="n">
         <v>6738.33875</v>
       </c>
-      <c r="C44" s="9" t="n">
+      <c r="C44" s="11" t="n">
         <v>5102.691060606061</v>
       </c>
-      <c r="D44" s="9" t="n">
+      <c r="D44" s="11" t="n">
         <v>6470.907857142856</v>
       </c>
-      <c r="E44" s="9" t="n">
+      <c r="E44" s="11" t="n">
         <v>6821.403333333333</v>
       </c>
-      <c r="F44" s="9" t="n">
+      <c r="F44" s="11" t="n">
         <v>6239.739999999999</v>
       </c>
-      <c r="G44" s="10" t="n">
+      <c r="G44" s="12" t="n">
         <v>6191.864791666666</v>
       </c>
     </row>
@@ -4058,20 +4086,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B45" s="9" t="n"/>
-      <c r="C45" s="9" t="n">
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n">
         <v>9123.4</v>
       </c>
-      <c r="D45" s="9" t="n">
+      <c r="D45" s="11" t="n">
         <v>4025.558333333333</v>
       </c>
-      <c r="E45" s="9" t="n">
+      <c r="E45" s="11" t="n">
         <v>6643.151666666667</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="11" t="n">
         <v>5040.430909090909</v>
       </c>
-      <c r="G45" s="10" t="n">
+      <c r="G45" s="12" t="n">
         <v>5643.044710144927</v>
       </c>
     </row>
@@ -4081,22 +4109,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B46" s="10" t="n">
+      <c r="B46" s="12" t="n">
         <v>8058.825873015874</v>
       </c>
-      <c r="C46" s="10" t="n">
+      <c r="C46" s="12" t="n">
         <v>5928.628333333333</v>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="12" t="n">
         <v>5709.363333333333</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="12" t="n">
         <v>6760.536507936507</v>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="12" t="n">
         <v>5652.173703703704</v>
       </c>
-      <c r="G46" s="10" t="n">
+      <c r="G46" s="13" t="n">
         <v>6477.896936026937</v>
       </c>
     </row>
@@ -4261,7 +4289,7 @@
       <c r="F6" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="7" t="n">
         <v>99</v>
       </c>
     </row>
@@ -4405,7 +4433,7 @@
       <c r="F14" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="7" t="n">
         <v>99</v>
       </c>
     </row>
@@ -4549,7 +4577,7 @@
       <c r="F22" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G22" s="7" t="n">
         <v>99</v>
       </c>
     </row>
@@ -4693,7 +4721,7 @@
       <c r="F30" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="G30" s="5" t="n">
+      <c r="G30" s="7" t="n">
         <v>45</v>
       </c>
     </row>
@@ -4837,7 +4865,7 @@
       <c r="F38" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="G38" s="7" t="n">
         <v>54</v>
       </c>
     </row>
@@ -4981,7 +5009,7 @@
       <c r="F46" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="G46" s="5" t="n">
+      <c r="G46" s="7" t="n">
         <v>99</v>
       </c>
     </row>
@@ -5037,22 +5065,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B51" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="8" t="n">
+      <c r="B51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5062,22 +5090,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="8" t="n">
+      <c r="B52" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5087,20 +5115,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B53" s="7" t="n"/>
-      <c r="C53" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="8" t="n">
+      <c r="B53" s="8" t="n"/>
+      <c r="C53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5110,22 +5138,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B54" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="8" t="n">
+      <c r="B54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5181,22 +5209,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B59" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="8" t="n">
+      <c r="B59" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5206,22 +5234,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B60" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="8" t="n">
+      <c r="B60" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5231,20 +5259,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B61" s="7" t="n"/>
-      <c r="C61" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="8" t="n">
+      <c r="B61" s="8" t="n"/>
+      <c r="C61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5254,22 +5282,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B62" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="8" t="n">
+      <c r="B62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5325,22 +5353,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B67" s="7" t="n">
+      <c r="B67" s="8" t="n">
         <v>0.3529411764705883</v>
       </c>
-      <c r="C67" s="7" t="n">
+      <c r="C67" s="8" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="D67" s="7" t="n">
+      <c r="D67" s="8" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="E67" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="8" t="n">
+      <c r="E67" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="9" t="n">
         <v>0.4166666666666667</v>
       </c>
     </row>
@@ -5350,22 +5378,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B68" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C68" s="7" t="n">
+      <c r="B68" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" s="8" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="D68" s="7" t="n">
+      <c r="D68" s="8" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="E68" s="7" t="n">
+      <c r="E68" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="F68" s="7" t="n">
+      <c r="F68" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="G68" s="8" t="n">
+      <c r="G68" s="9" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -5375,20 +5403,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B69" s="7" t="n"/>
-      <c r="C69" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="7" t="n">
+      <c r="B69" s="8" t="n"/>
+      <c r="C69" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="8" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="E69" s="7" t="n">
+      <c r="E69" s="8" t="n">
         <v>0.25</v>
       </c>
-      <c r="F69" s="7" t="n">
+      <c r="F69" s="8" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="G69" s="8" t="n">
+      <c r="G69" s="9" t="n">
         <v>0.3478260869565217</v>
       </c>
     </row>
@@ -5398,22 +5426,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B70" s="8" t="n">
+      <c r="B70" s="9" t="n">
         <v>0.4761904761904762</v>
       </c>
-      <c r="C70" s="8" t="n">
+      <c r="C70" s="9" t="n">
         <v>0.3461538461538461</v>
       </c>
-      <c r="D70" s="8" t="n">
+      <c r="D70" s="9" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="E70" s="8" t="n">
+      <c r="E70" s="9" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="F70" s="8" t="n">
+      <c r="F70" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="G70" s="8" t="n">
+      <c r="G70" s="10" t="n">
         <v>0.4545454545454545</v>
       </c>
     </row>
@@ -5469,22 +5497,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B75" s="7" t="n">
+      <c r="B75" s="8" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="C75" s="7" t="n">
+      <c r="C75" s="8" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="D75" s="7" t="n">
+      <c r="D75" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E75" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="8" t="n">
+      <c r="E75" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="9" t="n">
         <v>0.5833333333333334</v>
       </c>
     </row>
@@ -5494,22 +5522,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B76" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" s="7" t="n">
+      <c r="B76" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="8" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="D76" s="7" t="n">
+      <c r="D76" s="8" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="E76" s="7" t="n">
+      <c r="E76" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="F76" s="7" t="n">
+      <c r="F76" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="G76" s="8" t="n">
+      <c r="G76" s="9" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -5519,20 +5547,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B77" s="7" t="n"/>
-      <c r="C77" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" s="7" t="n">
+      <c r="B77" s="8" t="n"/>
+      <c r="C77" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E77" s="7" t="n">
+      <c r="E77" s="8" t="n">
         <v>0.75</v>
       </c>
-      <c r="F77" s="7" t="n">
+      <c r="F77" s="8" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="G77" s="8" t="n">
+      <c r="G77" s="9" t="n">
         <v>0.6521739130434783</v>
       </c>
     </row>
@@ -5542,22 +5570,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B78" s="8" t="n">
+      <c r="B78" s="9" t="n">
         <v>0.5238095238095238</v>
       </c>
-      <c r="C78" s="8" t="n">
+      <c r="C78" s="9" t="n">
         <v>0.6538461538461539</v>
       </c>
-      <c r="D78" s="8" t="n">
+      <c r="D78" s="9" t="n">
         <v>0.3846153846153846</v>
       </c>
-      <c r="E78" s="8" t="n">
+      <c r="E78" s="9" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="F78" s="8" t="n">
+      <c r="F78" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="G78" s="8" t="n">
+      <c r="G78" s="10" t="n">
         <v>0.5454545454545454</v>
       </c>
     </row>
@@ -5613,22 +5641,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B83" s="7" t="n">
+      <c r="B83" s="8" t="n">
         <v>0.3529411764705883</v>
       </c>
-      <c r="C83" s="7" t="n">
+      <c r="C83" s="8" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="D83" s="7" t="n">
+      <c r="D83" s="8" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="E83" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="8" t="n">
+      <c r="E83" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="9" t="n">
         <v>0.4166666666666667</v>
       </c>
     </row>
@@ -5638,22 +5666,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B84" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C84" s="7" t="n">
+      <c r="B84" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" s="8" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="D84" s="7" t="n">
+      <c r="D84" s="8" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="E84" s="7" t="n">
+      <c r="E84" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="F84" s="7" t="n">
+      <c r="F84" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="G84" s="8" t="n">
+      <c r="G84" s="9" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -5663,20 +5691,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B85" s="7" t="n"/>
-      <c r="C85" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="7" t="n">
+      <c r="B85" s="8" t="n"/>
+      <c r="C85" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="8" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="E85" s="7" t="n">
+      <c r="E85" s="8" t="n">
         <v>0.25</v>
       </c>
-      <c r="F85" s="7" t="n">
+      <c r="F85" s="8" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="G85" s="8" t="n">
+      <c r="G85" s="9" t="n">
         <v>0.3478260869565217</v>
       </c>
     </row>
@@ -5686,22 +5714,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B86" s="8" t="n">
+      <c r="B86" s="9" t="n">
         <v>0.4761904761904762</v>
       </c>
-      <c r="C86" s="8" t="n">
+      <c r="C86" s="9" t="n">
         <v>0.3461538461538461</v>
       </c>
-      <c r="D86" s="8" t="n">
+      <c r="D86" s="9" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="E86" s="8" t="n">
+      <c r="E86" s="9" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="F86" s="8" t="n">
+      <c r="F86" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="G86" s="8" t="n">
+      <c r="G86" s="10" t="n">
         <v>0.4545454545454545</v>
       </c>
     </row>
@@ -5757,22 +5785,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B91" s="7" t="n">
+      <c r="B91" s="8" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="C91" s="7" t="n">
+      <c r="C91" s="8" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="D91" s="7" t="n">
+      <c r="D91" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E91" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="8" t="n">
+      <c r="E91" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="9" t="n">
         <v>0.5833333333333334</v>
       </c>
     </row>
@@ -5782,22 +5810,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B92" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" s="7" t="n">
+      <c r="B92" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="8" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="D92" s="7" t="n">
+      <c r="D92" s="8" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="E92" s="7" t="n">
+      <c r="E92" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="F92" s="7" t="n">
+      <c r="F92" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="G92" s="8" t="n">
+      <c r="G92" s="9" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -5807,20 +5835,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B93" s="7" t="n"/>
-      <c r="C93" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D93" s="7" t="n">
+      <c r="B93" s="8" t="n"/>
+      <c r="C93" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E93" s="7" t="n">
+      <c r="E93" s="8" t="n">
         <v>0.75</v>
       </c>
-      <c r="F93" s="7" t="n">
+      <c r="F93" s="8" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="G93" s="8" t="n">
+      <c r="G93" s="9" t="n">
         <v>0.6521739130434783</v>
       </c>
     </row>
@@ -5830,22 +5858,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B94" s="8" t="n">
+      <c r="B94" s="9" t="n">
         <v>0.5238095238095238</v>
       </c>
-      <c r="C94" s="8" t="n">
+      <c r="C94" s="9" t="n">
         <v>0.6538461538461539</v>
       </c>
-      <c r="D94" s="8" t="n">
+      <c r="D94" s="9" t="n">
         <v>0.3846153846153846</v>
       </c>
-      <c r="E94" s="8" t="n">
+      <c r="E94" s="9" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="F94" s="8" t="n">
+      <c r="F94" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="G94" s="8" t="n">
+      <c r="G94" s="10" t="n">
         <v>0.5454545454545454</v>
       </c>
     </row>
@@ -5901,22 +5929,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B99" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C99" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D99" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F99" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G99" s="8" t="n">
+      <c r="B99" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5926,22 +5954,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B100" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C100" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D100" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G100" s="8" t="n">
+      <c r="B100" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5951,20 +5979,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B101" s="7" t="n"/>
-      <c r="C101" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D101" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F101" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G101" s="8" t="n">
+      <c r="B101" s="8" t="n"/>
+      <c r="C101" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5974,22 +6002,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B102" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C102" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D102" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F102" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" s="8" t="n">
+      <c r="B102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6234,16 +6262,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="n">
+      <c r="A2" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="D2" s="7" t="n">
+      <c r="D2" s="8" t="n">
         <v>0.1717171717171717</v>
       </c>
       <c r="E2" s="4" t="n">
@@ -6255,7 +6283,7 @@
       <c r="G2" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="H2" s="7" t="n">
+      <c r="H2" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I2" s="4" t="n">
@@ -6267,43 +6295,43 @@
       <c r="K2" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="L2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="9" t="n">
+      <c r="L2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="11" t="n">
         <v>17650</v>
       </c>
-      <c r="O2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="9" t="n">
+      <c r="O2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="11" t="n">
         <v>1068.43</v>
       </c>
-      <c r="Q2" s="9" t="n">
+      <c r="Q2" s="11" t="n">
         <v>17650</v>
       </c>
-      <c r="R2" s="7" t="n">
+      <c r="R2" s="8" t="n">
         <v>0.06053427762039661</v>
       </c>
-      <c r="S2" s="11" t="n">
+      <c r="S2" s="14" t="n">
         <v>0.0577928865222811</v>
       </c>
-      <c r="T2" s="9" t="n">
+      <c r="T2" s="11" t="n">
         <v>2580.882352941177</v>
       </c>
-      <c r="U2" s="9" t="n">
+      <c r="U2" s="11" t="n">
         <v>1361.764705882353</v>
       </c>
-      <c r="V2" s="9" t="n">
+      <c r="V2" s="11" t="n">
         <v>2365.427745098039</v>
       </c>
-      <c r="W2" s="9" t="n">
+      <c r="W2" s="11" t="n">
         <v>1910.793529411765</v>
       </c>
-      <c r="X2" s="9" t="n">
+      <c r="X2" s="11" t="n">
         <v>8369.528725490196</v>
       </c>
       <c r="Y2" s="4" t="n">
@@ -6324,39 +6352,39 @@
       <c r="AD2" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="AE2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG2" s="7" t="n">
+      <c r="AE2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="8" t="n">
         <v>0.3529411764705883</v>
       </c>
-      <c r="AH2" s="7" t="n">
+      <c r="AH2" s="8" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="AI2" s="7" t="n">
+      <c r="AI2" s="8" t="n">
         <v>0.3529411764705883</v>
       </c>
-      <c r="AJ2" s="7" t="n">
+      <c r="AJ2" s="8" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="AK2" s="7" t="n">
+      <c r="AK2" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="11" t="n">
+      <c r="A3" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="14" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="8" t="n">
         <v>0.1414141414141414</v>
       </c>
       <c r="E3" s="4" t="n">
@@ -6368,7 +6396,7 @@
       <c r="G3" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H3" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="4" t="n">
@@ -6380,43 +6408,43 @@
       <c r="K3" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="L3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="9" t="n">
+      <c r="L3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="11" t="n">
         <v>15575</v>
       </c>
-      <c r="O3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="9" t="n">
+      <c r="O3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="11" t="n">
         <v>15575</v>
       </c>
-      <c r="R3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="11" t="n">
+      <c r="R3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="14" t="n">
         <v>0.06610009615858989</v>
       </c>
-      <c r="T3" s="9" t="n">
+      <c r="T3" s="11" t="n">
         <v>1901.785714285714</v>
       </c>
-      <c r="U3" s="9" t="n">
+      <c r="U3" s="11" t="n">
         <v>1148.214285714286</v>
       </c>
-      <c r="V3" s="9" t="n">
+      <c r="V3" s="11" t="n">
         <v>1701.684523809524</v>
       </c>
-      <c r="W3" s="9" t="n">
+      <c r="W3" s="11" t="n">
         <v>1284.228214285714</v>
       </c>
-      <c r="X3" s="9" t="n">
+      <c r="X3" s="11" t="n">
         <v>6349.381071428571</v>
       </c>
       <c r="Y3" s="4" t="n">
@@ -6437,39 +6465,39 @@
       <c r="AD3" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="AE3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG3" s="7" t="n">
+      <c r="AE3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="8" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="AH3" s="7" t="n">
+      <c r="AH3" s="8" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="AI3" s="7" t="n">
+      <c r="AI3" s="8" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="AJ3" s="7" t="n">
+      <c r="AJ3" s="8" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="AK3" s="7" t="n">
+      <c r="AK3" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="11" t="n">
+      <c r="A4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="14" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="8" t="n">
         <v>0.0303030303030303</v>
       </c>
       <c r="E4" s="4" t="n">
@@ -6481,7 +6509,7 @@
       <c r="G4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="4" t="n">
@@ -6493,43 +6521,43 @@
       <c r="K4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="9" t="n">
+      <c r="L4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="11" t="n">
         <v>2650</v>
       </c>
-      <c r="O4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="9" t="n">
+      <c r="O4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="11" t="n">
         <v>2650</v>
       </c>
-      <c r="R4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="11" t="n">
+      <c r="R4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="14" t="n">
         <v>0.06689377519236493</v>
       </c>
-      <c r="T4" s="9" t="n">
+      <c r="T4" s="11" t="n">
         <v>3333.333333333333</v>
       </c>
-      <c r="U4" s="9" t="n">
+      <c r="U4" s="11" t="n">
         <v>883.3333333333334</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="11" t="n">
         <v>1263.166666666667</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="11" t="n">
         <v>891.9227777777779</v>
       </c>
-      <c r="X4" s="9" t="n">
+      <c r="X4" s="11" t="n">
         <v>5616.231111111109</v>
       </c>
       <c r="Y4" s="4" t="n">
@@ -6550,39 +6578,39 @@
       <c r="AD4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AE4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG4" s="7" t="n">
+      <c r="AE4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="8" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AH4" s="7" t="n">
+      <c r="AH4" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AI4" s="7" t="n">
+      <c r="AI4" s="8" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AJ4" s="7" t="n">
+      <c r="AJ4" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AK4" s="7" t="n">
+      <c r="AK4" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="11" t="n">
+      <c r="A5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="14" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="8" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="E5" s="4" t="n">
@@ -6594,7 +6622,7 @@
       <c r="G5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="4" t="n">
@@ -6606,43 +6634,43 @@
       <c r="K5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="9" t="n">
+      <c r="L5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="11" t="n">
         <v>1025</v>
       </c>
-      <c r="O5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="9" t="n">
+      <c r="O5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="11" t="n">
         <v>1025</v>
       </c>
-      <c r="R5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="11" t="n">
+      <c r="R5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="14" t="n">
         <v>0.0362809958464943</v>
       </c>
-      <c r="T5" s="9" t="n">
+      <c r="T5" s="11" t="n">
         <v>5000</v>
       </c>
-      <c r="U5" s="9" t="n">
+      <c r="U5" s="11" t="n">
         <v>1025</v>
       </c>
-      <c r="V5" s="9" t="n">
+      <c r="V5" s="11" t="n">
         <v>3401.775</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="11" t="n">
         <v>3148.925</v>
       </c>
-      <c r="X5" s="9" t="n">
+      <c r="X5" s="11" t="n">
         <v>6969.213333333333</v>
       </c>
       <c r="Y5" s="4" t="n">
@@ -6663,39 +6691,39 @@
       <c r="AD5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AE5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="7" t="n">
+      <c r="AE5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="11" t="n">
+      <c r="A6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="14" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="8" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="E6" s="4" t="n">
@@ -6707,7 +6735,7 @@
       <c r="G6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="4" t="n">
@@ -6719,43 +6747,43 @@
       <c r="K6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="9" t="n">
+      <c r="L6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="11" t="n">
         <v>1725</v>
       </c>
-      <c r="O6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="9" t="n">
+      <c r="O6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="11" t="n">
         <v>1725</v>
       </c>
-      <c r="R6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="11" t="n">
+      <c r="R6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="14" t="n">
         <v>0.0883014953417364</v>
       </c>
-      <c r="T6" s="9" t="n">
+      <c r="T6" s="11" t="n">
         <v>2800</v>
       </c>
-      <c r="U6" s="9" t="n">
+      <c r="U6" s="11" t="n">
         <v>1725</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="V6" s="11" t="n">
         <v>6621.896666666667</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="11" t="n">
         <v>5839.903333333333</v>
       </c>
-      <c r="X6" s="9" t="n">
+      <c r="X6" s="11" t="n">
         <v>8855.946666666665</v>
       </c>
       <c r="Y6" s="4" t="n">
@@ -6776,39 +6804,39 @@
       <c r="AD6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AE6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="7" t="n">
+      <c r="AE6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="8" t="n">
         <v>0.04040404040404041</v>
       </c>
       <c r="E7" s="4" t="n">
@@ -6820,7 +6848,7 @@
       <c r="G7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="4" t="n">
@@ -6832,43 +6860,43 @@
       <c r="K7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="9" t="n">
+      <c r="L7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="11" t="n">
         <v>3400</v>
       </c>
-      <c r="O7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="9" t="n">
+      <c r="O7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="11" t="n">
         <v>3400</v>
       </c>
-      <c r="R7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="11" t="n">
+      <c r="R7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="14" t="n">
         <v>0.06126832174503703</v>
       </c>
-      <c r="T7" s="9" t="n">
+      <c r="T7" s="11" t="n">
         <v>1875</v>
       </c>
-      <c r="U7" s="9" t="n">
+      <c r="U7" s="11" t="n">
         <v>850</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="11" t="n">
         <v>1813.700416666666</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="11" t="n">
         <v>1421.17625</v>
       </c>
-      <c r="X7" s="9" t="n">
+      <c r="X7" s="11" t="n">
         <v>6738.33875</v>
       </c>
       <c r="Y7" s="4" t="n">
@@ -6889,39 +6917,39 @@
       <c r="AD7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="AE7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="7" t="n">
+      <c r="AE7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="14" t="n">
         <v>2</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="8" t="n">
         <v>0.1111111111111111</v>
       </c>
       <c r="E8" s="4" t="n">
@@ -6933,7 +6961,7 @@
       <c r="G8" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="4" t="n">
@@ -6945,43 +6973,43 @@
       <c r="K8" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="9" t="n">
+      <c r="L8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="11" t="n">
         <v>10025</v>
       </c>
-      <c r="O8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="9" t="n">
+      <c r="O8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="11" t="n">
         <v>10025</v>
       </c>
-      <c r="R8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="11" t="n">
+      <c r="R8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="14" t="n">
         <v>0.06177054996739424</v>
       </c>
-      <c r="T8" s="9" t="n">
+      <c r="T8" s="11" t="n">
         <v>1988.636363636364</v>
       </c>
-      <c r="U8" s="9" t="n">
+      <c r="U8" s="11" t="n">
         <v>911.3636363636364</v>
       </c>
-      <c r="V8" s="9" t="n">
+      <c r="V8" s="11" t="n">
         <v>1019.511212121212</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" s="11" t="n">
         <v>717.9643939393939</v>
       </c>
-      <c r="X8" s="9" t="n">
+      <c r="X8" s="11" t="n">
         <v>5102.691060606061</v>
       </c>
       <c r="Y8" s="4" t="n">
@@ -7002,39 +7030,39 @@
       <c r="AD8" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="AE8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG8" s="7" t="n">
+      <c r="AE8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="8" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="AH8" s="7" t="n">
+      <c r="AH8" s="8" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="AI8" s="7" t="n">
+      <c r="AI8" s="8" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="AJ8" s="7" t="n">
+      <c r="AJ8" s="8" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="AK8" s="7" t="n">
+      <c r="AK8" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="14" t="n">
         <v>3</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="8" t="n">
         <v>0.0707070707070707</v>
       </c>
       <c r="E9" s="4" t="n">
@@ -7046,7 +7074,7 @@
       <c r="G9" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="4" t="n">
@@ -7058,43 +7086,43 @@
       <c r="K9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="L9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="9" t="n">
+      <c r="L9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="11" t="n">
         <v>6450</v>
       </c>
-      <c r="O9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="9" t="n">
+      <c r="O9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11" t="n">
         <v>6450</v>
       </c>
-      <c r="R9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="11" t="n">
+      <c r="R9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="14" t="n">
         <v>0.0563004874639454</v>
       </c>
-      <c r="T9" s="9" t="n">
+      <c r="T9" s="11" t="n">
         <v>2717.857142857143</v>
       </c>
-      <c r="U9" s="9" t="n">
+      <c r="U9" s="11" t="n">
         <v>921.4285714285714</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" s="11" t="n">
         <v>2609.839761904761</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W9" s="11" t="n">
         <v>2331.138333333333</v>
       </c>
-      <c r="X9" s="9" t="n">
+      <c r="X9" s="11" t="n">
         <v>6470.907857142856</v>
       </c>
       <c r="Y9" s="4" t="n">
@@ -7115,39 +7143,39 @@
       <c r="AD9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="AE9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG9" s="7" t="n">
+      <c r="AE9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="8" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="AH9" s="7" t="n">
+      <c r="AH9" s="8" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="AI9" s="7" t="n">
+      <c r="AI9" s="8" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="AJ9" s="7" t="n">
+      <c r="AJ9" s="8" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="AK9" s="7" t="n">
+      <c r="AK9" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="14" t="n">
         <v>4</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="8" t="n">
         <v>0.1212121212121212</v>
       </c>
       <c r="E10" s="4" t="n">
@@ -7159,7 +7187,7 @@
       <c r="G10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="8" t="n">
         <v>0.2</v>
       </c>
       <c r="I10" s="4" t="n">
@@ -7171,43 +7199,43 @@
       <c r="K10" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="L10" s="8" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="11" t="n">
         <v>2945.06</v>
       </c>
-      <c r="N10" s="9" t="n">
+      <c r="N10" s="11" t="n">
         <v>13625</v>
       </c>
-      <c r="O10" s="7" t="n">
+      <c r="O10" s="8" t="n">
         <v>0.2161511926605505</v>
       </c>
-      <c r="P10" s="9" t="n">
+      <c r="P10" s="11" t="n">
         <v>2647.62</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Q10" s="11" t="n">
         <v>13625</v>
       </c>
-      <c r="R10" s="7" t="n">
+      <c r="R10" s="8" t="n">
         <v>0.1943207339449541</v>
       </c>
-      <c r="S10" s="11" t="n">
+      <c r="S10" s="14" t="n">
         <v>0.06337038055148971</v>
       </c>
-      <c r="T10" s="9" t="n">
+      <c r="T10" s="11" t="n">
         <v>2537.5</v>
       </c>
-      <c r="U10" s="9" t="n">
+      <c r="U10" s="11" t="n">
         <v>1135.416666666667</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="11" t="n">
         <v>1927.416111111111</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="11" t="n">
         <v>1505.116527777777</v>
       </c>
-      <c r="X10" s="9" t="n">
+      <c r="X10" s="11" t="n">
         <v>6821.403333333333</v>
       </c>
       <c r="Y10" s="4" t="n">
@@ -7228,39 +7256,39 @@
       <c r="AD10" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AE10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="7" t="n">
+      <c r="AE10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH10" s="7" t="n">
+      <c r="AH10" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AI10" s="7" t="n">
+      <c r="AI10" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AJ10" s="7" t="n">
+      <c r="AJ10" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AK10" s="7" t="n">
+      <c r="AK10" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="14" t="n">
         <v>5</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="8" t="n">
         <v>0.06060606060606061</v>
       </c>
       <c r="E11" s="4" t="n">
@@ -7272,7 +7300,7 @@
       <c r="G11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="4" t="n">
@@ -7284,43 +7312,43 @@
       <c r="K11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="L11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="9" t="n">
+      <c r="L11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="11" t="n">
         <v>4225</v>
       </c>
-      <c r="O11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="9" t="n">
+      <c r="O11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="11" t="n">
         <v>352.94</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="11" t="n">
         <v>4225</v>
       </c>
-      <c r="R11" s="7" t="n">
+      <c r="R11" s="8" t="n">
         <v>0.08353609467455621</v>
       </c>
-      <c r="S11" s="11" t="n">
+      <c r="S11" s="14" t="n">
         <v>0.04846571286640807</v>
       </c>
-      <c r="T11" s="9" t="n">
+      <c r="T11" s="11" t="n">
         <v>1433.333333333333</v>
       </c>
-      <c r="U11" s="9" t="n">
+      <c r="U11" s="11" t="n">
         <v>704.1666666666666</v>
       </c>
-      <c r="V11" s="9" t="n">
+      <c r="V11" s="11" t="n">
         <v>1710.215</v>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="11" t="n">
         <v>1415.172777777778</v>
       </c>
-      <c r="X11" s="9" t="n">
+      <c r="X11" s="11" t="n">
         <v>6239.739999999999</v>
       </c>
       <c r="Y11" s="4" t="n">
@@ -7341,39 +7369,39 @@
       <c r="AD11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AE11" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="7" t="n">
+      <c r="AE11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH11" s="7" t="n">
+      <c r="AH11" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AI11" s="7" t="n">
+      <c r="AI11" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AJ11" s="7" t="n">
+      <c r="AJ11" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AK11" s="7" t="n">
+      <c r="AK11" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="14" t="n">
         <v>2</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="8" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="E12" s="4" t="n">
@@ -7385,7 +7413,7 @@
       <c r="G12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="4" t="n">
@@ -7397,43 +7425,43 @@
       <c r="K12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="9" t="n">
+      <c r="L12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="O12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="9" t="n">
+      <c r="O12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="R12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="11" t="n">
+      <c r="R12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="14" t="n">
         <v>0.0303980241284316</v>
       </c>
-      <c r="T12" s="9" t="n">
+      <c r="T12" s="11" t="n">
         <v>2050</v>
       </c>
-      <c r="U12" s="9" t="n">
+      <c r="U12" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="V12" s="9" t="n">
+      <c r="V12" s="11" t="n">
         <v>1990.17</v>
       </c>
-      <c r="W12" s="9" t="n">
+      <c r="W12" s="11" t="n">
         <v>1712.836666666667</v>
       </c>
-      <c r="X12" s="9" t="n">
+      <c r="X12" s="11" t="n">
         <v>9123.4</v>
       </c>
       <c r="Y12" s="4" t="n">
@@ -7454,39 +7482,39 @@
       <c r="AD12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AE12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK12" s="7" t="n">
+      <c r="AE12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK12" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="14" t="n">
         <v>3</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="8" t="n">
         <v>0.0303030303030303</v>
       </c>
       <c r="E13" s="4" t="n">
@@ -7498,7 +7526,7 @@
       <c r="G13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="4" t="n">
@@ -7510,43 +7538,43 @@
       <c r="K13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="9" t="n">
+      <c r="L13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="11" t="n">
         <v>2200</v>
       </c>
-      <c r="O13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="9" t="n">
+      <c r="O13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="11" t="n">
         <v>2200</v>
       </c>
-      <c r="R13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="11" t="n">
+      <c r="R13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="14" t="n">
         <v>0.07126428996341931</v>
       </c>
-      <c r="T13" s="9" t="n">
+      <c r="T13" s="11" t="n">
         <v>1000</v>
       </c>
-      <c r="U13" s="9" t="n">
+      <c r="U13" s="11" t="n">
         <v>733.3333333333334</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="11" t="n">
         <v>1002.82</v>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" s="11" t="n">
         <v>721.4566666666666</v>
       </c>
-      <c r="X13" s="9" t="n">
+      <c r="X13" s="11" t="n">
         <v>4025.558333333333</v>
       </c>
       <c r="Y13" s="4" t="n">
@@ -7567,39 +7595,39 @@
       <c r="AD13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AE13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG13" s="7" t="n">
+      <c r="AE13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="8" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AH13" s="7" t="n">
+      <c r="AH13" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AI13" s="7" t="n">
+      <c r="AI13" s="8" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AJ13" s="7" t="n">
+      <c r="AJ13" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AK13" s="7" t="n">
+      <c r="AK13" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="14" t="n">
         <v>4</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="8" t="n">
         <v>0.08080808080808081</v>
       </c>
       <c r="E14" s="4" t="n">
@@ -7611,7 +7639,7 @@
       <c r="G14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="H14" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="4" t="n">
@@ -7623,43 +7651,43 @@
       <c r="K14" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="L14" s="8" t="n">
         <v>0.125</v>
       </c>
-      <c r="M14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="9" t="n">
+      <c r="M14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="11" t="n">
         <v>7125</v>
       </c>
-      <c r="O14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="9" t="n">
+      <c r="O14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="11" t="n">
         <v>7125</v>
       </c>
-      <c r="R14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="11" t="n">
+      <c r="R14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="14" t="n">
         <v>0.05258242726948031</v>
       </c>
-      <c r="T14" s="9" t="n">
+      <c r="T14" s="11" t="n">
         <v>2775</v>
       </c>
-      <c r="U14" s="9" t="n">
+      <c r="U14" s="11" t="n">
         <v>890.625</v>
       </c>
-      <c r="V14" s="9" t="n">
+      <c r="V14" s="11" t="n">
         <v>2654.001458333333</v>
       </c>
-      <c r="W14" s="9" t="n">
+      <c r="W14" s="11" t="n">
         <v>2348.330833333333</v>
       </c>
-      <c r="X14" s="9" t="n">
+      <c r="X14" s="11" t="n">
         <v>6643.151666666667</v>
       </c>
       <c r="Y14" s="4" t="n">
@@ -7680,39 +7708,39 @@
       <c r="AD14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG14" s="7" t="n">
+      <c r="AE14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="8" t="n">
         <v>0.25</v>
       </c>
-      <c r="AH14" s="7" t="n">
+      <c r="AH14" s="8" t="n">
         <v>0.75</v>
       </c>
-      <c r="AI14" s="7" t="n">
+      <c r="AI14" s="8" t="n">
         <v>0.25</v>
       </c>
-      <c r="AJ14" s="7" t="n">
+      <c r="AJ14" s="8" t="n">
         <v>0.75</v>
       </c>
-      <c r="AK14" s="7" t="n">
+      <c r="AK14" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="14" t="n">
         <v>5</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="8" t="n">
         <v>0.1111111111111111</v>
       </c>
       <c r="E15" s="4" t="n">
@@ -7724,7 +7752,7 @@
       <c r="G15" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="H15" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="I15" s="4" t="n">
@@ -7736,43 +7764,43 @@
       <c r="K15" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="L15" s="7" t="n">
+      <c r="L15" s="8" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="11" t="n">
         <v>1495.57</v>
       </c>
-      <c r="N15" s="9" t="n">
+      <c r="N15" s="11" t="n">
         <v>7925</v>
       </c>
-      <c r="O15" s="7" t="n">
+      <c r="O15" s="8" t="n">
         <v>0.1887154574132492</v>
       </c>
-      <c r="P15" s="9" t="n">
+      <c r="P15" s="11" t="n">
         <v>2122.93</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="11" t="n">
         <v>7925</v>
       </c>
-      <c r="R15" s="7" t="n">
+      <c r="R15" s="8" t="n">
         <v>0.2678776025236593</v>
       </c>
-      <c r="S15" s="11" t="n">
+      <c r="S15" s="14" t="n">
         <v>0.05840024437431996</v>
       </c>
-      <c r="T15" s="9" t="n">
+      <c r="T15" s="11" t="n">
         <v>1586.363636363636</v>
       </c>
-      <c r="U15" s="9" t="n">
+      <c r="U15" s="11" t="n">
         <v>720.4545454545455</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="11" t="n">
         <v>1592.921515151515</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="11" t="n">
         <v>1322.805151515151</v>
       </c>
-      <c r="X15" s="9" t="n">
+      <c r="X15" s="11" t="n">
         <v>5040.430909090909</v>
       </c>
       <c r="Y15" s="4" t="n">
@@ -7793,25 +7821,25 @@
       <c r="AD15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="AE15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG15" s="7" t="n">
+      <c r="AE15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="8" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="AH15" s="7" t="n">
+      <c r="AH15" s="8" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="AI15" s="7" t="n">
+      <c r="AI15" s="8" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="AJ15" s="7" t="n">
+      <c r="AJ15" s="8" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="AK15" s="7" t="n">
+      <c r="AK15" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8050,13 +8078,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n">
+      <c r="A2" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="8" t="n">
         <v>0.3636363636363636</v>
       </c>
       <c r="D2" s="4" t="n">
@@ -8068,7 +8096,7 @@
       <c r="F2" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="G2" s="7" t="n">
+      <c r="G2" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="4" t="n">
@@ -8080,43 +8108,43 @@
       <c r="J2" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="K2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="9" t="n">
+      <c r="K2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="11" t="n">
         <v>38625</v>
       </c>
-      <c r="N2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="9" t="n">
+      <c r="N2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="11" t="n">
         <v>1068.43</v>
       </c>
-      <c r="P2" s="9" t="n">
+      <c r="P2" s="11" t="n">
         <v>38625</v>
       </c>
-      <c r="Q2" s="7" t="n">
+      <c r="Q2" s="8" t="n">
         <v>0.02766161812297735</v>
       </c>
-      <c r="R2" s="11" t="n">
+      <c r="R2" s="14" t="n">
         <v>0.06203178427401005</v>
       </c>
-      <c r="S2" s="9" t="n">
+      <c r="S2" s="11" t="n">
         <v>2452.777777777778</v>
       </c>
-      <c r="T2" s="9" t="n">
+      <c r="T2" s="11" t="n">
         <v>1239.583333333333</v>
       </c>
-      <c r="U2" s="9" t="n">
+      <c r="U2" s="11" t="n">
         <v>2162.472962962963</v>
       </c>
-      <c r="V2" s="9" t="n">
+      <c r="V2" s="11" t="n">
         <v>1725.757824074074</v>
       </c>
-      <c r="W2" s="9" t="n">
+      <c r="W2" s="11" t="n">
         <v>7329.088240740742</v>
       </c>
       <c r="X2" s="4" t="n">
@@ -8137,36 +8165,36 @@
       <c r="AC2" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="AD2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" s="7" t="n">
+      <c r="AD2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="8" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="AG2" s="7" t="n">
+      <c r="AG2" s="8" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="AH2" s="7" t="n">
+      <c r="AH2" s="8" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="AI2" s="7" t="n">
+      <c r="AI2" s="8" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="AJ2" s="7" t="n">
+      <c r="AJ2" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n">
+      <c r="A3" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="8" t="n">
         <v>0.404040404040404</v>
       </c>
       <c r="D3" s="4" t="n">
@@ -8178,7 +8206,7 @@
       <c r="F3" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="G3" s="8" t="n">
         <v>0.05714285714285714</v>
       </c>
       <c r="H3" s="4" t="n">
@@ -8190,43 +8218,43 @@
       <c r="J3" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="K3" s="7" t="n">
+      <c r="K3" s="8" t="n">
         <v>0.025</v>
       </c>
-      <c r="L3" s="9" t="n">
+      <c r="L3" s="11" t="n">
         <v>2945.06</v>
       </c>
-      <c r="M3" s="9" t="n">
+      <c r="M3" s="11" t="n">
         <v>37725</v>
       </c>
-      <c r="N3" s="7" t="n">
+      <c r="N3" s="8" t="n">
         <v>0.07806653412856196</v>
       </c>
-      <c r="O3" s="9" t="n">
+      <c r="O3" s="11" t="n">
         <v>3000.56</v>
       </c>
-      <c r="P3" s="9" t="n">
+      <c r="P3" s="11" t="n">
         <v>37725</v>
       </c>
-      <c r="Q3" s="7" t="n">
+      <c r="Q3" s="8" t="n">
         <v>0.0795377070907886</v>
       </c>
-      <c r="R3" s="11" t="n">
+      <c r="R3" s="14" t="n">
         <v>0.05924728981713567</v>
       </c>
-      <c r="S3" s="9" t="n">
+      <c r="S3" s="11" t="n">
         <v>2186.25</v>
       </c>
-      <c r="T3" s="9" t="n">
+      <c r="T3" s="11" t="n">
         <v>943.125</v>
       </c>
-      <c r="U3" s="9" t="n">
+      <c r="U3" s="11" t="n">
         <v>1753.214666666667</v>
       </c>
-      <c r="V3" s="9" t="n">
+      <c r="V3" s="11" t="n">
         <v>1411.317916666666</v>
       </c>
-      <c r="W3" s="9" t="n">
+      <c r="W3" s="11" t="n">
         <v>6191.864791666666</v>
       </c>
       <c r="X3" s="4" t="n">
@@ -8247,36 +8275,36 @@
       <c r="AC3" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="AD3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" s="7" t="n">
+      <c r="AD3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="8" t="n">
         <v>0.55</v>
       </c>
-      <c r="AG3" s="7" t="n">
+      <c r="AG3" s="8" t="n">
         <v>0.45</v>
       </c>
-      <c r="AH3" s="7" t="n">
+      <c r="AH3" s="8" t="n">
         <v>0.55</v>
       </c>
-      <c r="AI3" s="7" t="n">
+      <c r="AI3" s="8" t="n">
         <v>0.45</v>
       </c>
-      <c r="AJ3" s="7" t="n">
+      <c r="AJ3" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="n">
+      <c r="A4" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="8" t="n">
         <v>0.2323232323232323</v>
       </c>
       <c r="D4" s="4" t="n">
@@ -8288,7 +8316,7 @@
       <c r="F4" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="8" t="n">
         <v>0.1363636363636364</v>
       </c>
       <c r="H4" s="4" t="n">
@@ -8300,43 +8328,43 @@
       <c r="J4" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="K4" s="7" t="n">
+      <c r="K4" s="8" t="n">
         <v>0.1304347826086956</v>
       </c>
-      <c r="L4" s="9" t="n">
+      <c r="L4" s="11" t="n">
         <v>1495.57</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" s="11" t="n">
         <v>17750</v>
       </c>
-      <c r="N4" s="7" t="n">
+      <c r="N4" s="8" t="n">
         <v>0.08425746478873239</v>
       </c>
-      <c r="O4" s="9" t="n">
+      <c r="O4" s="11" t="n">
         <v>2122.93</v>
       </c>
-      <c r="P4" s="9" t="n">
+      <c r="P4" s="11" t="n">
         <v>17750</v>
       </c>
-      <c r="Q4" s="7" t="n">
+      <c r="Q4" s="8" t="n">
         <v>0.1196016901408451</v>
       </c>
-      <c r="R4" s="11" t="n">
+      <c r="R4" s="14" t="n">
         <v>0.05683708696921964</v>
       </c>
-      <c r="S4" s="9" t="n">
+      <c r="S4" s="11" t="n">
         <v>1943.478260869565</v>
       </c>
-      <c r="T4" s="9" t="n">
+      <c r="T4" s="11" t="n">
         <v>771.7391304347826</v>
       </c>
-      <c r="U4" s="9" t="n">
+      <c r="U4" s="11" t="n">
         <v>1902.294710144928</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="11" t="n">
         <v>1618.030869565217</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="11" t="n">
         <v>5643.044710144927</v>
       </c>
       <c r="X4" s="4" t="n">
@@ -8357,25 +8385,25 @@
       <c r="AC4" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="AD4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" s="7" t="n">
+      <c r="AD4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="8" t="n">
         <v>0.3478260869565217</v>
       </c>
-      <c r="AG4" s="7" t="n">
+      <c r="AG4" s="8" t="n">
         <v>0.6521739130434783</v>
       </c>
-      <c r="AH4" s="7" t="n">
+      <c r="AH4" s="8" t="n">
         <v>0.3478260869565217</v>
       </c>
-      <c r="AI4" s="7" t="n">
+      <c r="AI4" s="8" t="n">
         <v>0.6521739130434783</v>
       </c>
-      <c r="AJ4" s="7" t="n">
+      <c r="AJ4" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8614,13 +8642,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n">
+      <c r="A2" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="8" t="n">
         <v>0.2121212121212121</v>
       </c>
       <c r="D2" s="4" t="n">
@@ -8632,7 +8660,7 @@
       <c r="F2" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G2" s="7" t="n">
+      <c r="G2" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="4" t="n">
@@ -8644,43 +8672,43 @@
       <c r="J2" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="K2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="9" t="n">
+      <c r="K2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="11" t="n">
         <v>21050</v>
       </c>
-      <c r="N2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="9" t="n">
+      <c r="N2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="11" t="n">
         <v>1068.43</v>
       </c>
-      <c r="P2" s="9" t="n">
+      <c r="P2" s="11" t="n">
         <v>21050</v>
       </c>
-      <c r="Q2" s="7" t="n">
+      <c r="Q2" s="8" t="n">
         <v>0.05075676959619953</v>
       </c>
-      <c r="R2" s="11" t="n">
+      <c r="R2" s="14" t="n">
         <v>0.0584548741837584</v>
       </c>
-      <c r="S2" s="9" t="n">
+      <c r="S2" s="11" t="n">
         <v>2446.428571428572</v>
       </c>
-      <c r="T2" s="9" t="n">
+      <c r="T2" s="11" t="n">
         <v>1264.285714285714</v>
       </c>
-      <c r="U2" s="9" t="n">
+      <c r="U2" s="11" t="n">
         <v>2260.336825396825</v>
       </c>
-      <c r="V2" s="9" t="n">
+      <c r="V2" s="11" t="n">
         <v>1817.533095238095</v>
       </c>
-      <c r="W2" s="9" t="n">
+      <c r="W2" s="11" t="n">
         <v>8058.825873015874</v>
       </c>
       <c r="X2" s="4" t="n">
@@ -8701,36 +8729,36 @@
       <c r="AC2" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="AD2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" s="7" t="n">
+      <c r="AD2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="8" t="n">
         <v>0.4761904761904762</v>
       </c>
-      <c r="AG2" s="7" t="n">
+      <c r="AG2" s="8" t="n">
         <v>0.5238095238095238</v>
       </c>
-      <c r="AH2" s="7" t="n">
+      <c r="AH2" s="8" t="n">
         <v>0.4761904761904762</v>
       </c>
-      <c r="AI2" s="7" t="n">
+      <c r="AI2" s="8" t="n">
         <v>0.5238095238095238</v>
       </c>
-      <c r="AJ2" s="7" t="n">
+      <c r="AJ2" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n">
+      <c r="A3" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="8" t="n">
         <v>0.2626262626262627</v>
       </c>
       <c r="D3" s="4" t="n">
@@ -8742,7 +8770,7 @@
       <c r="F3" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="G3" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="4" t="n">
@@ -8754,43 +8782,43 @@
       <c r="J3" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="K3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="9" t="n">
+      <c r="K3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="11" t="n">
         <v>26100</v>
       </c>
-      <c r="N3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="9" t="n">
+      <c r="N3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="11" t="n">
         <v>26100</v>
       </c>
-      <c r="Q3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="11" t="n">
+      <c r="Q3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="14" t="n">
         <v>0.06289520846115487</v>
       </c>
-      <c r="S3" s="9" t="n">
+      <c r="S3" s="11" t="n">
         <v>1944.230769230769</v>
       </c>
-      <c r="T3" s="9" t="n">
+      <c r="T3" s="11" t="n">
         <v>1023.076923076923</v>
       </c>
-      <c r="U3" s="9" t="n">
+      <c r="U3" s="11" t="n">
         <v>1424.168333333333</v>
       </c>
-      <c r="V3" s="9" t="n">
+      <c r="V3" s="11" t="n">
         <v>1061.14</v>
       </c>
-      <c r="W3" s="9" t="n">
+      <c r="W3" s="11" t="n">
         <v>5928.628333333333</v>
       </c>
       <c r="X3" s="4" t="n">
@@ -8811,36 +8839,36 @@
       <c r="AC3" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="AD3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" s="7" t="n">
+      <c r="AD3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="8" t="n">
         <v>0.3461538461538461</v>
       </c>
-      <c r="AG3" s="7" t="n">
+      <c r="AG3" s="8" t="n">
         <v>0.6538461538461539</v>
       </c>
-      <c r="AH3" s="7" t="n">
+      <c r="AH3" s="8" t="n">
         <v>0.3461538461538461</v>
       </c>
-      <c r="AI3" s="7" t="n">
+      <c r="AI3" s="8" t="n">
         <v>0.6538461538461539</v>
       </c>
-      <c r="AJ3" s="7" t="n">
+      <c r="AJ3" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="n">
+      <c r="A4" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="8" t="n">
         <v>0.1313131313131313</v>
       </c>
       <c r="D4" s="4" t="n">
@@ -8852,7 +8880,7 @@
       <c r="F4" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="4" t="n">
@@ -8864,43 +8892,43 @@
       <c r="J4" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="K4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="9" t="n">
+      <c r="K4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="11" t="n">
         <v>11300</v>
       </c>
-      <c r="N4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="9" t="n">
+      <c r="N4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="11" t="n">
         <v>11300</v>
       </c>
-      <c r="Q4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="11" t="n">
+      <c r="Q4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="14" t="n">
         <v>0.0621982775165362</v>
       </c>
-      <c r="S4" s="9" t="n">
+      <c r="S4" s="11" t="n">
         <v>2463.461538461539</v>
       </c>
-      <c r="T4" s="9" t="n">
+      <c r="T4" s="11" t="n">
         <v>869.2307692307693</v>
       </c>
-      <c r="U4" s="9" t="n">
+      <c r="U4" s="11" t="n">
         <v>1928.218333333333</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="11" t="n">
         <v>1627.546666666666</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="11" t="n">
         <v>5709.363333333333</v>
       </c>
       <c r="X4" s="4" t="n">
@@ -8921,36 +8949,36 @@
       <c r="AC4" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="AD4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" s="7" t="n">
+      <c r="AD4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="8" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="AG4" s="7" t="n">
+      <c r="AG4" s="8" t="n">
         <v>0.3846153846153846</v>
       </c>
-      <c r="AH4" s="7" t="n">
+      <c r="AH4" s="8" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="AI4" s="7" t="n">
+      <c r="AI4" s="8" t="n">
         <v>0.3846153846153846</v>
       </c>
-      <c r="AJ4" s="7" t="n">
+      <c r="AJ4" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="8" t="n">
         <v>0.2121212121212121</v>
       </c>
       <c r="D5" s="4" t="n">
@@ -8962,7 +8990,7 @@
       <c r="F5" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="8" t="n">
         <v>0.1052631578947368</v>
       </c>
       <c r="H5" s="4" t="n">
@@ -8974,43 +9002,43 @@
       <c r="J5" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="K5" s="7" t="n">
+      <c r="K5" s="8" t="n">
         <v>0.09523809523809523</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="11" t="n">
         <v>2945.06</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="M5" s="11" t="n">
         <v>21775</v>
       </c>
-      <c r="N5" s="7" t="n">
+      <c r="N5" s="8" t="n">
         <v>0.135249598163031</v>
       </c>
-      <c r="O5" s="9" t="n">
+      <c r="O5" s="11" t="n">
         <v>2647.62</v>
       </c>
-      <c r="P5" s="9" t="n">
+      <c r="P5" s="11" t="n">
         <v>21775</v>
       </c>
-      <c r="Q5" s="7" t="n">
+      <c r="Q5" s="8" t="n">
         <v>0.1215898966704937</v>
       </c>
-      <c r="R5" s="11" t="n">
+      <c r="R5" s="14" t="n">
         <v>0.05797071336286728</v>
       </c>
-      <c r="S5" s="9" t="n">
+      <c r="S5" s="11" t="n">
         <v>2745.238095238095</v>
       </c>
-      <c r="T5" s="9" t="n">
+      <c r="T5" s="11" t="n">
         <v>1036.904761904762</v>
       </c>
-      <c r="U5" s="9" t="n">
+      <c r="U5" s="11" t="n">
         <v>2274.418095238095</v>
       </c>
-      <c r="V5" s="9" t="n">
+      <c r="V5" s="11" t="n">
         <v>1904.617619047619</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="11" t="n">
         <v>6760.536507936507</v>
       </c>
       <c r="X5" s="4" t="n">
@@ -9031,36 +9059,36 @@
       <c r="AC5" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="AD5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" s="7" t="n">
+      <c r="AD5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="8" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="AG5" s="7" t="n">
+      <c r="AG5" s="8" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="AH5" s="7" t="n">
+      <c r="AH5" s="8" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="AI5" s="7" t="n">
+      <c r="AI5" s="8" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="AJ5" s="7" t="n">
+      <c r="AJ5" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>0.1818181818181818</v>
       </c>
       <c r="D6" s="4" t="n">
@@ -9072,7 +9100,7 @@
       <c r="F6" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <v>0.1764705882352941</v>
       </c>
       <c r="H6" s="4" t="n">
@@ -9084,43 +9112,43 @@
       <c r="J6" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="K6" s="7" t="n">
+      <c r="K6" s="8" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="11" t="n">
         <v>1495.57</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="11" t="n">
         <v>13875</v>
       </c>
-      <c r="N6" s="7" t="n">
+      <c r="N6" s="8" t="n">
         <v>0.1077888288288288</v>
       </c>
-      <c r="O6" s="9" t="n">
+      <c r="O6" s="11" t="n">
         <v>2475.87</v>
       </c>
-      <c r="P6" s="9" t="n">
+      <c r="P6" s="11" t="n">
         <v>13875</v>
       </c>
-      <c r="Q6" s="7" t="n">
+      <c r="Q6" s="8" t="n">
         <v>0.1784410810810811</v>
       </c>
-      <c r="R6" s="11" t="n">
+      <c r="R6" s="14" t="n">
         <v>0.05674991448098357</v>
       </c>
-      <c r="S6" s="9" t="n">
+      <c r="S6" s="11" t="n">
         <v>1602.777777777778</v>
       </c>
-      <c r="T6" s="9" t="n">
+      <c r="T6" s="11" t="n">
         <v>770.8333333333334</v>
       </c>
-      <c r="U6" s="9" t="n">
+      <c r="U6" s="11" t="n">
         <v>1911.406851851852</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="V6" s="11" t="n">
         <v>1604.544259259259</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="11" t="n">
         <v>5652.173703703704</v>
       </c>
       <c r="X6" s="4" t="n">
@@ -9141,25 +9169,25 @@
       <c r="AC6" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="AD6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF6" s="7" t="n">
+      <c r="AD6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AG6" s="7" t="n">
+      <c r="AG6" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH6" s="7" t="n">
+      <c r="AH6" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AI6" s="7" t="n">
+      <c r="AI6" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AJ6" s="7" t="n">
+      <c r="AJ6" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9395,7 +9423,7 @@
       <c r="A2" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="n">
@@ -9407,7 +9435,7 @@
       <c r="E2" s="4" t="n">
         <v>81</v>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="F2" s="8" t="n">
         <v>0.05813953488372093</v>
       </c>
       <c r="G2" s="4" t="n">
@@ -9419,43 +9447,43 @@
       <c r="I2" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="J2" s="7" t="n">
+      <c r="J2" s="8" t="n">
         <v>0.04081632653061224</v>
       </c>
-      <c r="K2" s="9" t="n">
+      <c r="K2" s="11" t="n">
         <v>4440.63</v>
       </c>
-      <c r="L2" s="9" t="n">
+      <c r="L2" s="11" t="n">
         <v>94100</v>
       </c>
-      <c r="M2" s="7" t="n">
+      <c r="M2" s="8" t="n">
         <v>0.04719054197662062</v>
       </c>
-      <c r="N2" s="9" t="n">
+      <c r="N2" s="11" t="n">
         <v>6191.92</v>
       </c>
-      <c r="O2" s="9" t="n">
+      <c r="O2" s="11" t="n">
         <v>94100</v>
       </c>
-      <c r="P2" s="7" t="n">
+      <c r="P2" s="8" t="n">
         <v>0.06580148777895856</v>
       </c>
-      <c r="Q2" s="11" t="n">
+      <c r="Q2" s="14" t="n">
         <v>0.05969988713981658</v>
       </c>
-      <c r="R2" s="9" t="n">
+      <c r="R2" s="11" t="n">
         <v>2226.767676767677</v>
       </c>
-      <c r="S2" s="9" t="n">
+      <c r="S2" s="11" t="n">
         <v>1011.111111111111</v>
       </c>
-      <c r="T2" s="9" t="n">
+      <c r="T2" s="11" t="n">
         <v>1936.670622895623</v>
       </c>
-      <c r="U2" s="9" t="n">
+      <c r="U2" s="11" t="n">
         <v>1573.683922558922</v>
       </c>
-      <c r="V2" s="9" t="n">
+      <c r="V2" s="11" t="n">
         <v>6477.896936026937</v>
       </c>
       <c r="W2" s="4" t="n">
@@ -9476,25 +9504,25 @@
       <c r="AB2" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="AC2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="7" t="n">
+      <c r="AC2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="8" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="AF2" s="7" t="n">
+      <c r="AF2" s="8" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="AG2" s="7" t="n">
+      <c r="AG2" s="8" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="AH2" s="7" t="n">
+      <c r="AH2" s="8" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="AI2" s="7" t="n">
+      <c r="AI2" s="8" t="n">
         <v>1</v>
       </c>
     </row>

--- a/output/model_analysis_20260429/model_bin_risk_performance_pivot.xlsx
+++ b/output/model_analysis_20260429/model_bin_risk_performance_pivot.xlsx
@@ -9,13 +9,15 @@
   <sheets>
     <sheet name="metric_guide" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="risk_perf" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="amount_risk" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="profile" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="conversion" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="raw_cross_metrics" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="raw_row_totals" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="raw_column_totals" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="raw_grand_total" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="risk_perf_manual" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="amount_risk" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="profile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="profile_deal_sample" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="conversion" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="raw_cross_metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="raw_row_totals" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="raw_column_totals" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="raw_grand_total" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1194,16 +1196,1351 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AJ8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="37" customWidth="1" min="12" max="12"/>
+    <col width="39" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="38" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="27" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="31" customWidth="1" min="27" max="27"/>
+    <col width="33" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="29" max="29"/>
+    <col width="17" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="21" customWidth="1" min="34" max="34"/>
+    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="20" customWidth="1" min="36" max="36"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>comparison_model_score_bin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sample_cnt</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sample_pct</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_valid_cnt</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_bad_cnt</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_good_cnt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_bad_rate</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_valid_cnt</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_bad_cnt</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_good_cnt</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_bad_rate</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_amount_overdue_amount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_amount_principal_amount</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_amount_overdue_rate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_amount_overdue_amount</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_amount_principal_amount</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_amount_overdue_rate</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>avg_PTI</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>avg_requested_loan_amount</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>avg_total_amount</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>avg_gross_surplus</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>avg_net_surplus</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>avg_total_income</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>apply_cnt</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>completed_application_cnt</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>approved_application_cnt</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>auto_approved_application_cnt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>manual_approved_application_cnt</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>deal_sample_cnt</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>completion_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>approval_rate</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>auto_approval_rate</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>manual_approval_rate</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>auto_approval_share</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>manual_approval_share</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>deal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>3405</v>
+      </c>
+      <c r="C2" s="8" t="n">
+        <v>0.02158601758578936</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="K2" s="8" t="n">
+        <v>0.06944444444444445</v>
+      </c>
+      <c r="L2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="11" t="n">
+        <v>86950</v>
+      </c>
+      <c r="N2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="11" t="n">
+        <v>10366.75</v>
+      </c>
+      <c r="P2" s="11" t="n">
+        <v>86950</v>
+      </c>
+      <c r="Q2" s="8" t="n">
+        <v>0.1192265669925244</v>
+      </c>
+      <c r="R2" s="14" t="n">
+        <v>0.04193792693892595</v>
+      </c>
+      <c r="S2" s="11" t="n">
+        <v>1834.001762114538</v>
+      </c>
+      <c r="T2" s="11" t="n">
+        <v>1207.638888888889</v>
+      </c>
+      <c r="U2" s="11" t="n">
+        <v>-487.8318722466961</v>
+      </c>
+      <c r="V2" s="11" t="n">
+        <v>-905.5644292706803</v>
+      </c>
+      <c r="W2" s="11" t="n">
+        <v>1117.251026921194</v>
+      </c>
+      <c r="X2" s="4" t="n">
+        <v>3405</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>3405</v>
+      </c>
+      <c r="Z2" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="AA2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB2" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="AC2" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="AD2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="8" t="n">
+        <v>0.02320117474302496</v>
+      </c>
+      <c r="AF2" s="8" t="n">
+        <v>0.000881057268722467</v>
+      </c>
+      <c r="AG2" s="8" t="n">
+        <v>0.0223201174743025</v>
+      </c>
+      <c r="AH2" s="8" t="n">
+        <v>0.0379746835443038</v>
+      </c>
+      <c r="AI2" s="8" t="n">
+        <v>0.9620253164556962</v>
+      </c>
+      <c r="AJ2" s="8" t="n">
+        <v>0.9113924050632911</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>30048</v>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>0.1904894732504549</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>3961</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>268</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>3693</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>0.06765968189851047</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>7498</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>249</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>7249</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>0.03320885569485196</v>
+      </c>
+      <c r="L3" s="11" t="n">
+        <v>327244.2500000001</v>
+      </c>
+      <c r="M3" s="11" t="n">
+        <v>10817326</v>
+      </c>
+      <c r="N3" s="8" t="n">
+        <v>0.03025186168929364</v>
+      </c>
+      <c r="O3" s="11" t="n">
+        <v>488405.03</v>
+      </c>
+      <c r="P3" s="11" t="n">
+        <v>10817326</v>
+      </c>
+      <c r="Q3" s="8" t="n">
+        <v>0.04515025524792356</v>
+      </c>
+      <c r="R3" s="14" t="n">
+        <v>0.05066055472132761</v>
+      </c>
+      <c r="S3" s="11" t="n">
+        <v>2308.134451544196</v>
+      </c>
+      <c r="T3" s="11" t="n">
+        <v>1354.09438679835</v>
+      </c>
+      <c r="U3" s="11" t="n">
+        <v>177.0520408457579</v>
+      </c>
+      <c r="V3" s="11" t="n">
+        <v>-144.5270471689741</v>
+      </c>
+      <c r="W3" s="11" t="n">
+        <v>6252.549996283725</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>30048</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>30048</v>
+      </c>
+      <c r="Z3" s="4" t="n">
+        <v>9480</v>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <v>2887</v>
+      </c>
+      <c r="AB3" s="4" t="n">
+        <v>6593</v>
+      </c>
+      <c r="AC3" s="4" t="n">
+        <v>7999</v>
+      </c>
+      <c r="AD3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="8" t="n">
+        <v>0.3154952076677316</v>
+      </c>
+      <c r="AF3" s="8" t="n">
+        <v>0.09607960596379127</v>
+      </c>
+      <c r="AG3" s="8" t="n">
+        <v>0.2194156017039404</v>
+      </c>
+      <c r="AH3" s="8" t="n">
+        <v>0.3045358649789029</v>
+      </c>
+      <c r="AI3" s="8" t="n">
+        <v>0.6954641350210971</v>
+      </c>
+      <c r="AJ3" s="8" t="n">
+        <v>0.8437763713080169</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>30047</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>0.1904831337445559</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>3365</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>2995</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>0.1099554234769688</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>6351</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>421</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>5930</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>0.06628877342150842</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>396241.16</v>
+      </c>
+      <c r="M4" s="11" t="n">
+        <v>6982597</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>0.05674696105188371</v>
+      </c>
+      <c r="O4" s="11" t="n">
+        <v>558630.89</v>
+      </c>
+      <c r="P4" s="11" t="n">
+        <v>6982597</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>0.08000331252111499</v>
+      </c>
+      <c r="R4" s="14" t="n">
+        <v>0.0455235489904727</v>
+      </c>
+      <c r="S4" s="11" t="n">
+        <v>2104.14214397444</v>
+      </c>
+      <c r="T4" s="11" t="n">
+        <v>1035.788951421801</v>
+      </c>
+      <c r="U4" s="11" t="n">
+        <v>563.000201573091</v>
+      </c>
+      <c r="V4" s="11" t="n">
+        <v>270.4526173994076</v>
+      </c>
+      <c r="W4" s="11" t="n">
+        <v>5550.268271374846</v>
+      </c>
+      <c r="X4" s="4" t="n">
+        <v>30047</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>30047</v>
+      </c>
+      <c r="Z4" s="4" t="n">
+        <v>8002</v>
+      </c>
+      <c r="AA4" s="4" t="n">
+        <v>2669</v>
+      </c>
+      <c r="AB4" s="4" t="n">
+        <v>5333</v>
+      </c>
+      <c r="AC4" s="4" t="n">
+        <v>6752</v>
+      </c>
+      <c r="AD4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="8" t="n">
+        <v>0.2663161047691949</v>
+      </c>
+      <c r="AF4" s="8" t="n">
+        <v>0.08882750357772823</v>
+      </c>
+      <c r="AG4" s="8" t="n">
+        <v>0.1774886011914667</v>
+      </c>
+      <c r="AH4" s="8" t="n">
+        <v>0.3335416145963509</v>
+      </c>
+      <c r="AI4" s="8" t="n">
+        <v>0.6664583854036491</v>
+      </c>
+      <c r="AJ4" s="8" t="n">
+        <v>0.8437890527368158</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>30047</v>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>0.1904831337445559</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>2533</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>382</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>2151</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>0.1508093170153968</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>4089</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>386</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>3703</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>0.09439960870628515</v>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>368557.58</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>3927842</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>0.09383207878524644</v>
+      </c>
+      <c r="O5" s="11" t="n">
+        <v>469589.6799999999</v>
+      </c>
+      <c r="P5" s="11" t="n">
+        <v>3927842</v>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>0.1195541164843189</v>
+      </c>
+      <c r="R5" s="14" t="n">
+        <v>0.0431086190525217</v>
+      </c>
+      <c r="S5" s="11" t="n">
+        <v>1960.415449129697</v>
+      </c>
+      <c r="T5" s="11" t="n">
+        <v>912.9047397769517</v>
+      </c>
+      <c r="U5" s="11" t="n">
+        <v>915.48970107942</v>
+      </c>
+      <c r="V5" s="11" t="n">
+        <v>627.7629505996161</v>
+      </c>
+      <c r="W5" s="11" t="n">
+        <v>5243.57630906025</v>
+      </c>
+      <c r="X5" s="4" t="n">
+        <v>30047</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>30047</v>
+      </c>
+      <c r="Z5" s="4" t="n">
+        <v>5075</v>
+      </c>
+      <c r="AA5" s="4" t="n">
+        <v>1691</v>
+      </c>
+      <c r="AB5" s="4" t="n">
+        <v>3384</v>
+      </c>
+      <c r="AC5" s="4" t="n">
+        <v>4304</v>
+      </c>
+      <c r="AD5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="8" t="n">
+        <v>0.1689020534495956</v>
+      </c>
+      <c r="AF5" s="8" t="n">
+        <v>0.05627849702133324</v>
+      </c>
+      <c r="AG5" s="8" t="n">
+        <v>0.1126235564282624</v>
+      </c>
+      <c r="AH5" s="8" t="n">
+        <v>0.3332019704433498</v>
+      </c>
+      <c r="AI5" s="8" t="n">
+        <v>0.6667980295566502</v>
+      </c>
+      <c r="AJ5" s="8" t="n">
+        <v>0.8480788177339902</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>30047</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>0.1904831337445559</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>1552</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>277</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1275</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>0.178479381443299</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>1965</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>191</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>1774</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>0.09720101781170483</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>244019.8</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>1886233</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>0.1293688531586501</v>
+      </c>
+      <c r="O6" s="11" t="n">
+        <v>286950.21</v>
+      </c>
+      <c r="P6" s="11" t="n">
+        <v>1886233</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>0.1521287189864667</v>
+      </c>
+      <c r="R6" s="14" t="n">
+        <v>0.04251180572340477</v>
+      </c>
+      <c r="S6" s="11" t="n">
+        <v>1857.072053782407</v>
+      </c>
+      <c r="T6" s="11" t="n">
+        <v>959.9150127226463</v>
+      </c>
+      <c r="U6" s="11" t="n">
+        <v>736.9061559112944</v>
+      </c>
+      <c r="V6" s="11" t="n">
+        <v>441.8838940104946</v>
+      </c>
+      <c r="W6" s="11" t="n">
+        <v>4643.697768606961</v>
+      </c>
+      <c r="X6" s="4" t="n">
+        <v>30047</v>
+      </c>
+      <c r="Y6" s="4" t="n">
+        <v>30047</v>
+      </c>
+      <c r="Z6" s="4" t="n">
+        <v>2262</v>
+      </c>
+      <c r="AA6" s="4" t="n">
+        <v>597</v>
+      </c>
+      <c r="AB6" s="4" t="n">
+        <v>1665</v>
+      </c>
+      <c r="AC6" s="4" t="n">
+        <v>1965</v>
+      </c>
+      <c r="AD6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="8" t="n">
+        <v>0.07528205810896263</v>
+      </c>
+      <c r="AF6" s="8" t="n">
+        <v>0.01986887210037608</v>
+      </c>
+      <c r="AG6" s="8" t="n">
+        <v>0.05541318600858654</v>
+      </c>
+      <c r="AH6" s="8" t="n">
+        <v>0.2639257294429708</v>
+      </c>
+      <c r="AI6" s="8" t="n">
+        <v>0.7360742705570292</v>
+      </c>
+      <c r="AJ6" s="8" t="n">
+        <v>0.8687002652519894</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>30047</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>0.1904831337445559</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1576</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>0.2639593908629442</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1969</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>1675</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>0.1493143727780599</v>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>341067.65</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>1730989</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>0.1970362896586864</v>
+      </c>
+      <c r="O7" s="11" t="n">
+        <v>386468.5700000001</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>1730989</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>0.2232646019125483</v>
+      </c>
+      <c r="R7" s="14" t="n">
+        <v>0.03809913111359703</v>
+      </c>
+      <c r="S7" s="11" t="n">
+        <v>1722.414716943455</v>
+      </c>
+      <c r="T7" s="11" t="n">
+        <v>879.1208735398679</v>
+      </c>
+      <c r="U7" s="11" t="n">
+        <v>1368.75337016452</v>
+      </c>
+      <c r="V7" s="11" t="n">
+        <v>1104.727413330227</v>
+      </c>
+      <c r="W7" s="11" t="n">
+        <v>5644.138230383509</v>
+      </c>
+      <c r="X7" s="4" t="n">
+        <v>30047</v>
+      </c>
+      <c r="Y7" s="4" t="n">
+        <v>30047</v>
+      </c>
+      <c r="Z7" s="4" t="n">
+        <v>2207</v>
+      </c>
+      <c r="AA7" s="4" t="n">
+        <v>297</v>
+      </c>
+      <c r="AB7" s="4" t="n">
+        <v>1910</v>
+      </c>
+      <c r="AC7" s="4" t="n">
+        <v>1969</v>
+      </c>
+      <c r="AD7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="8" t="n">
+        <v>0.07345159250507538</v>
+      </c>
+      <c r="AF7" s="8" t="n">
+        <v>0.009884514260991115</v>
+      </c>
+      <c r="AG7" s="8" t="n">
+        <v>0.06356707824408427</v>
+      </c>
+      <c r="AH7" s="8" t="n">
+        <v>0.1345718169460806</v>
+      </c>
+      <c r="AI7" s="8" t="n">
+        <v>0.8654281830539193</v>
+      </c>
+      <c r="AJ7" s="8" t="n">
+        <v>0.8921613049388309</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n"/>
+      <c r="B8" s="4" t="n">
+        <v>4100</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>0.02599197418553198</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>165</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="L8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>231300</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="11" t="n">
+        <v>10504.48</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>231300</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>0.04541495892779939</v>
+      </c>
+      <c r="R8" s="14" t="n">
+        <v>0.0500500976841957</v>
+      </c>
+      <c r="S8" s="11" t="n">
+        <v>1876.664878048781</v>
+      </c>
+      <c r="T8" s="11" t="n">
+        <v>1257.065217391304</v>
+      </c>
+      <c r="U8" s="11" t="n">
+        <v>-563.9332463414636</v>
+      </c>
+      <c r="V8" s="11" t="n">
+        <v>-958.8505967479674</v>
+      </c>
+      <c r="W8" s="11" t="n">
+        <v>1581.861180487805</v>
+      </c>
+      <c r="X8" s="4" t="n">
+        <v>4100</v>
+      </c>
+      <c r="Y8" s="4" t="n">
+        <v>4100</v>
+      </c>
+      <c r="Z8" s="4" t="n">
+        <v>208</v>
+      </c>
+      <c r="AA8" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AB8" s="4" t="n">
+        <v>163</v>
+      </c>
+      <c r="AC8" s="4" t="n">
+        <v>184</v>
+      </c>
+      <c r="AD8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="8" t="n">
+        <v>0.05073170731707317</v>
+      </c>
+      <c r="AF8" s="8" t="n">
+        <v>0.01097560975609756</v>
+      </c>
+      <c r="AG8" s="8" t="n">
+        <v>0.03975609756097561</v>
+      </c>
+      <c r="AH8" s="8" t="n">
+        <v>0.2163461538461539</v>
+      </c>
+      <c r="AI8" s="8" t="n">
+        <v>0.7836538461538461</v>
+      </c>
+      <c r="AJ8" s="8" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AI2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="37" customWidth="1" min="11" max="11"/>
+    <col width="39" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="38" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="27" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="31" customWidth="1" min="26" max="26"/>
+    <col width="33" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="29" max="29"/>
+    <col width="21" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="21" customWidth="1" min="33" max="33"/>
+    <col width="23" customWidth="1" min="34" max="34"/>
+    <col width="20" customWidth="1" min="35" max="35"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sample_cnt</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sample_pct</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_valid_cnt</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_bad_cnt</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_good_cnt</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_bad_rate</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_valid_cnt</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_bad_cnt</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_good_cnt</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_bad_rate</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_amount_overdue_amount</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_amount_principal_amount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_amount_overdue_rate</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_amount_overdue_amount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_amount_principal_amount</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_amount_overdue_rate</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>avg_PTI</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>avg_requested_loan_amount</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>avg_total_amount</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>avg_gross_surplus</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>avg_net_surplus</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>avg_total_income</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>apply_cnt</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>completed_application_cnt</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>approved_application_cnt</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>auto_approved_application_cnt</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>manual_approved_application_cnt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>deal_sample_cnt</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>completion_rate</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>approval_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>auto_approval_rate</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>manual_approval_rate</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>auto_approval_share</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>manual_approval_share</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>deal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>157741</v>
+      </c>
+      <c r="B2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>12989</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>1713</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>11276</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>0.1318808222341982</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>22120</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>1557</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>20563</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>0.0703887884267631</v>
+      </c>
+      <c r="K2" s="11" t="n">
+        <v>1677130.44</v>
+      </c>
+      <c r="L2" s="11" t="n">
+        <v>25663237</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>0.06535147690059519</v>
+      </c>
+      <c r="N2" s="11" t="n">
+        <v>2210915.61</v>
+      </c>
+      <c r="O2" s="11" t="n">
+        <v>25663237</v>
+      </c>
+      <c r="P2" s="8" t="n">
+        <v>0.08615108101912475</v>
+      </c>
+      <c r="Q2" s="14" t="n">
+        <v>0.04598536943533157</v>
+      </c>
+      <c r="R2" s="11" t="n">
+        <v>1984.103860125142</v>
+      </c>
+      <c r="S2" s="11" t="n">
+        <v>1105.169369756937</v>
+      </c>
+      <c r="T2" s="11" t="n">
+        <v>691.2584792370616</v>
+      </c>
+      <c r="U2" s="11" t="n">
+        <v>393.6974539382066</v>
+      </c>
+      <c r="V2" s="11" t="n">
+        <v>5271.982231918143</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>157741</v>
+      </c>
+      <c r="X2" s="4" t="n">
+        <v>157741</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>27313</v>
+      </c>
+      <c r="Z2" s="4" t="n">
+        <v>8189</v>
+      </c>
+      <c r="AA2" s="4" t="n">
+        <v>19124</v>
+      </c>
+      <c r="AB2" s="4" t="n">
+        <v>23245</v>
+      </c>
+      <c r="AC2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="8" t="n">
+        <v>0.1731509246169353</v>
+      </c>
+      <c r="AE2" s="8" t="n">
+        <v>0.05191421380617595</v>
+      </c>
+      <c r="AF2" s="8" t="n">
+        <v>0.1212367108107594</v>
+      </c>
+      <c r="AG2" s="8" t="n">
+        <v>0.2998205982499176</v>
+      </c>
+      <c r="AH2" s="8" t="n">
+        <v>0.7001794017500824</v>
+      </c>
+      <c r="AI2" s="8" t="n">
+        <v>0.8510599348295683</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -1217,7 +2554,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>duedate_3m_30_valid_cnt</t>
+          <t>auto bin - 全量申请样本交叉分布</t>
         </is>
       </c>
     </row>
@@ -1275,28 +2612,28 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1</v>
+        <v>3075</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0</v>
+        <v>2885</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>1</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="4">
@@ -1306,28 +2643,28 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2850</v>
+        <v>16208</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1377</v>
+        <v>7840</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>655</v>
+        <v>3721</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>245</v>
+        <v>1501</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>128</v>
+        <v>786</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>5256</v>
+        <v>30314</v>
       </c>
     </row>
     <row r="5">
@@ -1337,28 +2674,28 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>859</v>
+        <v>8199</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1247</v>
+        <v>9095</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>887</v>
+        <v>6521</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>454</v>
+        <v>3720</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>290</v>
+        <v>2458</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>3737</v>
+        <v>30314</v>
       </c>
     </row>
     <row r="6">
@@ -1368,28 +2705,28 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>211</v>
+        <v>4067</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>554</v>
+        <v>7299</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>639</v>
+        <v>7809</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>441</v>
+        <v>6053</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>430</v>
+        <v>4785</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>2275</v>
+        <v>30314</v>
       </c>
     </row>
     <row r="7">
@@ -1399,28 +2736,28 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>40</v>
+        <v>1281</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>171</v>
+        <v>4319</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>291</v>
+        <v>7153</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>300</v>
+        <v>9016</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>450</v>
+        <v>8241</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>1252</v>
+        <v>30314</v>
       </c>
     </row>
     <row r="8">
@@ -1430,28 +2767,28 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>16</v>
+        <v>1447</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>61</v>
+        <v>4797</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>112</v>
+        <v>9717</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>278</v>
+        <v>13740</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>468</v>
+        <v>30314</v>
       </c>
     </row>
     <row r="9">
@@ -1461,28 +2798,28 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>2</v>
+        <v>3405</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3961</v>
+        <v>30048</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>3365</v>
+        <v>30047</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2533</v>
+        <v>30047</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1552</v>
+        <v>30047</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1576</v>
+        <v>30047</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>12989</v>
+        <v>157741</v>
       </c>
     </row>
     <row r="10"/>
@@ -1490,7 +2827,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>duedate_3m_30_bad_cnt</t>
+          <t>auto bin - duedate_3m_30_valid_cnt</t>
         </is>
       </c>
     </row>
@@ -1548,7 +2885,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0</v>
@@ -1569,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1579,28 +2916,28 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>182</v>
+        <v>2850</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>134</v>
+        <v>1377</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>83</v>
+        <v>655</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>27</v>
+        <v>245</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>21</v>
+        <v>128</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>447</v>
+        <v>5256</v>
       </c>
     </row>
     <row r="16">
@@ -1613,25 +2950,25 @@
         <v>0</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>63</v>
+        <v>859</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>142</v>
+        <v>1247</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>123</v>
+        <v>887</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>70</v>
+        <v>454</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>66</v>
+        <v>290</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>464</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="17">
@@ -1644,25 +2981,25 @@
         <v>0</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>64</v>
+        <v>554</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>105</v>
+        <v>639</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>85</v>
+        <v>441</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>100</v>
+        <v>430</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>373</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="18">
@@ -1675,25 +3012,25 @@
         <v>0</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>26</v>
+        <v>171</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>56</v>
+        <v>291</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>69</v>
+        <v>300</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>136</v>
+        <v>450</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>291</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="19">
@@ -1706,25 +3043,25 @@
         <v>0</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>93</v>
+        <v>278</v>
       </c>
       <c r="H19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>138</v>
+        <v>468</v>
       </c>
     </row>
     <row r="20">
@@ -1734,28 +3071,28 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>268</v>
+        <v>3961</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>370</v>
+        <v>3365</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>382</v>
+        <v>2533</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>277</v>
+        <v>1552</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>416</v>
+        <v>1576</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1713</v>
+        <v>12989</v>
       </c>
     </row>
     <row r="21"/>
@@ -1763,7 +3100,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>duedate_3m_30_good_cnt</t>
+          <t>auto bin - duedate_3m_30_bad_cnt</t>
         </is>
       </c>
     </row>
@@ -1821,7 +3158,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0</v>
@@ -1842,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1852,28 +3189,28 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2668</v>
+        <v>182</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1243</v>
+        <v>134</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>572</v>
+        <v>83</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>218</v>
+        <v>27</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="H26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>4809</v>
+        <v>447</v>
       </c>
     </row>
     <row r="27">
@@ -1886,25 +3223,25 @@
         <v>0</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>796</v>
+        <v>63</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1105</v>
+        <v>142</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>764</v>
+        <v>123</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>384</v>
+        <v>70</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>224</v>
+        <v>66</v>
       </c>
       <c r="H27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>3273</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28">
@@ -1917,25 +3254,25 @@
         <v>0</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>192</v>
+        <v>19</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>490</v>
+        <v>64</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>534</v>
+        <v>105</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>356</v>
+        <v>85</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>330</v>
+        <v>100</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>1902</v>
+        <v>373</v>
       </c>
     </row>
     <row r="29">
@@ -1948,25 +3285,25 @@
         <v>0</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>145</v>
+        <v>26</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>235</v>
+        <v>56</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>231</v>
+        <v>69</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>314</v>
+        <v>136</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>961</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30">
@@ -1979,25 +3316,25 @@
         <v>0</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>185</v>
+        <v>93</v>
       </c>
       <c r="H30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>330</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
@@ -2007,28 +3344,28 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>3693</v>
+        <v>268</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>2995</v>
+        <v>370</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>2151</v>
+        <v>382</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>1275</v>
+        <v>277</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>1160</v>
+        <v>416</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>11276</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="32"/>
@@ -2036,7 +3373,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>duedate_3m_30_bad_rate</t>
+          <t>auto bin - duedate_3m_30_good_cnt</t>
         </is>
       </c>
     </row>
@@ -2093,17 +3430,29 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="B36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="9" t="n">
-        <v>0</v>
+      <c r="B36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2112,27 +3461,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B37" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="8" t="n">
-        <v>0.06385964912280702</v>
-      </c>
-      <c r="D37" s="8" t="n">
-        <v>0.09731299927378359</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>0.1267175572519084</v>
-      </c>
-      <c r="F37" s="8" t="n">
-        <v>0.1102040816326531</v>
-      </c>
-      <c r="G37" s="8" t="n">
-        <v>0.1640625</v>
-      </c>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="9" t="n">
-        <v>0.08504566210045662</v>
+      <c r="B37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>2668</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>1243</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>572</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>218</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>4809</v>
       </c>
     </row>
     <row r="38">
@@ -2141,25 +3492,29 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="8" t="n">
-        <v>0.07334109429569266</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>0.1138732959101844</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>0.1386696730552424</v>
-      </c>
-      <c r="F38" s="8" t="n">
-        <v>0.1541850220264317</v>
-      </c>
-      <c r="G38" s="8" t="n">
-        <v>0.2275862068965517</v>
-      </c>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="9" t="n">
-        <v>0.1241637677281242</v>
+      <c r="B38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>796</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>764</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>384</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>224</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>3273</v>
       </c>
     </row>
     <row r="39">
@@ -2168,25 +3523,29 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="8" t="n">
-        <v>0.09004739336492891</v>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>0.1155234657039711</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>0.1643192488262911</v>
-      </c>
-      <c r="F39" s="8" t="n">
-        <v>0.1927437641723356</v>
-      </c>
-      <c r="G39" s="8" t="n">
-        <v>0.2325581395348837</v>
-      </c>
-      <c r="H39" s="8" t="n"/>
-      <c r="I39" s="9" t="n">
-        <v>0.163956043956044</v>
+      <c r="B39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>192</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>490</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>534</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>356</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>330</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>1902</v>
       </c>
     </row>
     <row r="40">
@@ -2195,25 +3554,29 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>0.152046783625731</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>0.1924398625429553</v>
-      </c>
-      <c r="F40" s="8" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>0.3022222222222222</v>
-      </c>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="9" t="n">
-        <v>0.2324281150159744</v>
+      <c r="B40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>231</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>314</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>961</v>
       </c>
     </row>
     <row r="41">
@@ -2222,25 +3585,29 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B41" s="8" t="n"/>
-      <c r="C41" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>0.2459016393442623</v>
-      </c>
-      <c r="F41" s="8" t="n">
-        <v>0.2321428571428572</v>
-      </c>
-      <c r="G41" s="8" t="n">
-        <v>0.3345323741007194</v>
-      </c>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="9" t="n">
-        <v>0.2948717948717949</v>
+      <c r="B41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>330</v>
       </c>
     </row>
     <row r="42">
@@ -2249,27 +3616,29 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="9" t="n">
-        <v>0.06765968189851047</v>
-      </c>
-      <c r="D42" s="9" t="n">
-        <v>0.1099554234769688</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>0.1508093170153968</v>
-      </c>
-      <c r="F42" s="9" t="n">
-        <v>0.178479381443299</v>
-      </c>
-      <c r="G42" s="9" t="n">
-        <v>0.2639593908629442</v>
-      </c>
-      <c r="H42" s="9" t="n"/>
-      <c r="I42" s="10" t="n">
-        <v>0.1318808222341982</v>
+      <c r="B42" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>3693</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>2995</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>2151</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>1275</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>1160</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>11276</v>
       </c>
     </row>
     <row r="43"/>
@@ -2277,7 +3646,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>duedate_1m_5_valid_cnt</t>
+          <t>auto bin - duedate_3m_30_bad_rate</t>
         </is>
       </c>
     </row>
@@ -2334,29 +3703,17 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="B47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="5" t="n">
-        <v>1</v>
+      <c r="B47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="8" t="n"/>
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2365,29 +3722,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B48" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>5148</v>
-      </c>
-      <c r="D48" s="4" t="n">
-        <v>2452</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>1002</v>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>306</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>152</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="I48" s="5" t="n">
-        <v>9150</v>
+      <c r="B48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>0.06385964912280702</v>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>0.09731299927378359</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>0.1267175572519084</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>0.1102040816326531</v>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>0.1640625</v>
+      </c>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="9" t="n">
+        <v>0.08504566210045662</v>
       </c>
     </row>
     <row r="49">
@@ -2396,29 +3751,25 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B49" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>1780</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>2316</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>1383</v>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>566</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>360</v>
-      </c>
-      <c r="H49" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>6476</v>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n">
+        <v>0.07334109429569266</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>0.1138732959101844</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>0.1386696730552424</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>0.1541850220264317</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>0.2275862068965517</v>
+      </c>
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="9" t="n">
+        <v>0.1241637677281242</v>
       </c>
     </row>
     <row r="50">
@@ -2427,29 +3778,25 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B50" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>473</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>1148</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>1050</v>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>550</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>521</v>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I50" s="5" t="n">
-        <v>3783</v>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8" t="n">
+        <v>0.09004739336492891</v>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>0.1155234657039711</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>0.1643192488262911</v>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>0.1927437641723356</v>
+      </c>
+      <c r="G50" s="8" t="n">
+        <v>0.2325581395348837</v>
+      </c>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="9" t="n">
+        <v>0.163956043956044</v>
       </c>
     </row>
     <row r="51">
@@ -2458,29 +3805,25 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B51" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>378</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>534</v>
-      </c>
-      <c r="F51" s="4" t="n">
-        <v>403</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>574</v>
-      </c>
-      <c r="H51" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I51" s="5" t="n">
-        <v>2011</v>
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>0.152046783625731</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0.1924398625429553</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>0.3022222222222222</v>
+      </c>
+      <c r="H51" s="8" t="n"/>
+      <c r="I51" s="9" t="n">
+        <v>0.2324281150159744</v>
       </c>
     </row>
     <row r="52">
@@ -2489,29 +3832,25 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B52" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="G52" s="4" t="n">
-        <v>362</v>
-      </c>
-      <c r="H52" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="I52" s="5" t="n">
-        <v>699</v>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0.2459016393442623</v>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>0.2321428571428572</v>
+      </c>
+      <c r="G52" s="8" t="n">
+        <v>0.3345323741007194</v>
+      </c>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="9" t="n">
+        <v>0.2948717948717949</v>
       </c>
     </row>
     <row r="53">
@@ -2520,29 +3859,27 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B53" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>7498</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>6351</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>4089</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>1965</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>1969</v>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>176</v>
-      </c>
-      <c r="I53" s="7" t="n">
-        <v>22120</v>
+      <c r="B53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>0.06765968189851047</v>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>0.1099554234769688</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>0.1508093170153968</v>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>0.178479381443299</v>
+      </c>
+      <c r="G53" s="9" t="n">
+        <v>0.2639593908629442</v>
+      </c>
+      <c r="H53" s="9" t="n"/>
+      <c r="I53" s="10" t="n">
+        <v>0.1318808222341982</v>
       </c>
     </row>
     <row r="54"/>
@@ -2550,7 +3887,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>duedate_1m_5_bad_cnt</t>
+          <t>auto bin - duedate_1m_5_valid_cnt</t>
         </is>
       </c>
     </row>
@@ -2608,7 +3945,7 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58" s="4" t="n">
         <v>0</v>
@@ -2629,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2639,28 +3976,28 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>151</v>
+        <v>5148</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>135</v>
+        <v>2452</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>75</v>
+        <v>1002</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>18</v>
+        <v>306</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>402</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="60">
@@ -2670,28 +4007,28 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>63</v>
+        <v>1780</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>133</v>
+        <v>2316</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>116</v>
+        <v>1383</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>56</v>
+        <v>566</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>42</v>
+        <v>360</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>415</v>
+        <v>6476</v>
       </c>
     </row>
     <row r="61">
@@ -2701,28 +4038,28 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>26</v>
+        <v>473</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>97</v>
+        <v>1148</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>117</v>
+        <v>1050</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>52</v>
+        <v>550</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>72</v>
+        <v>521</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>365</v>
+        <v>3783</v>
       </c>
     </row>
     <row r="62">
@@ -2732,28 +4069,28 @@
         </is>
       </c>
       <c r="B62" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>44</v>
+        <v>378</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>59</v>
+        <v>534</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>50</v>
+        <v>403</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>92</v>
+        <v>574</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>257</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="63">
@@ -2763,28 +4100,28 @@
         </is>
       </c>
       <c r="B63" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>69</v>
+        <v>362</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>118</v>
+        <v>699</v>
       </c>
     </row>
     <row r="64">
@@ -2794,28 +4131,28 @@
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>249</v>
+        <v>7498</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>421</v>
+        <v>6351</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>386</v>
+        <v>4089</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>191</v>
+        <v>1965</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>294</v>
+        <v>1969</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>11</v>
+        <v>176</v>
       </c>
       <c r="I64" s="7" t="n">
-        <v>1557</v>
+        <v>22120</v>
       </c>
     </row>
     <row r="65"/>
@@ -2823,7 +4160,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>duedate_1m_5_good_cnt</t>
+          <t>auto bin - duedate_1m_5_bad_cnt</t>
         </is>
       </c>
     </row>
@@ -2881,7 +4218,7 @@
         </is>
       </c>
       <c r="B69" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C69" s="4" t="n">
         <v>0</v>
@@ -2902,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2912,28 +4249,28 @@
         </is>
       </c>
       <c r="B70" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>4997</v>
+        <v>151</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>2317</v>
+        <v>135</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>927</v>
+        <v>75</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>288</v>
+        <v>18</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>133</v>
+        <v>19</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>8748</v>
+        <v>402</v>
       </c>
     </row>
     <row r="71">
@@ -2943,28 +4280,28 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>1717</v>
+        <v>63</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>2183</v>
+        <v>133</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>1267</v>
+        <v>116</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>510</v>
+        <v>56</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>318</v>
+        <v>42</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>6061</v>
+        <v>415</v>
       </c>
     </row>
     <row r="72">
@@ -2974,28 +4311,28 @@
         </is>
       </c>
       <c r="B72" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>447</v>
+        <v>26</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1051</v>
+        <v>97</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>933</v>
+        <v>117</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>498</v>
+        <v>52</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>449</v>
+        <v>72</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>3418</v>
+        <v>365</v>
       </c>
     </row>
     <row r="73">
@@ -3005,28 +4342,28 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>334</v>
+        <v>44</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>475</v>
+        <v>59</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>353</v>
+        <v>50</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>482</v>
+        <v>92</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>1754</v>
+        <v>257</v>
       </c>
     </row>
     <row r="74">
@@ -3036,28 +4373,28 @@
         </is>
       </c>
       <c r="B74" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>293</v>
+        <v>69</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>581</v>
+        <v>118</v>
       </c>
     </row>
     <row r="75">
@@ -3067,28 +4404,28 @@
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>7249</v>
+        <v>249</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>5930</v>
+        <v>421</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>3703</v>
+        <v>386</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>1774</v>
+        <v>191</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>1675</v>
+        <v>294</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>165</v>
+        <v>11</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>20563</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="76"/>
@@ -3096,7 +4433,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>duedate_1m_5_bad_rate</t>
+          <t>auto bin - duedate_1m_5_good_cnt</t>
         </is>
       </c>
     </row>
@@ -3153,17 +4490,29 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="B80" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="n"/>
-      <c r="E80" s="8" t="n"/>
-      <c r="F80" s="8" t="n"/>
-      <c r="G80" s="8" t="n"/>
-      <c r="H80" s="8" t="n"/>
-      <c r="I80" s="9" t="n">
-        <v>0</v>
+      <c r="B80" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -3172,29 +4521,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B81" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C81" s="8" t="n">
-        <v>0.02933177933177933</v>
-      </c>
-      <c r="D81" s="8" t="n">
-        <v>0.05505709624796085</v>
-      </c>
-      <c r="E81" s="8" t="n">
-        <v>0.0748502994011976</v>
-      </c>
-      <c r="F81" s="8" t="n">
-        <v>0.05882352941176471</v>
-      </c>
-      <c r="G81" s="8" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="H81" s="8" t="n">
-        <v>0.05714285714285714</v>
-      </c>
-      <c r="I81" s="9" t="n">
-        <v>0.0439344262295082</v>
+      <c r="B81" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>4997</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>2317</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>927</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>8748</v>
       </c>
     </row>
     <row r="82">
@@ -3203,29 +4552,29 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B82" s="8" t="n">
-        <v>0.04761904761904762</v>
-      </c>
-      <c r="C82" s="8" t="n">
-        <v>0.03539325842696629</v>
-      </c>
-      <c r="D82" s="8" t="n">
-        <v>0.057426597582038</v>
-      </c>
-      <c r="E82" s="8" t="n">
-        <v>0.08387563268257411</v>
-      </c>
-      <c r="F82" s="8" t="n">
-        <v>0.0989399293286219</v>
-      </c>
-      <c r="G82" s="8" t="n">
-        <v>0.1166666666666667</v>
-      </c>
-      <c r="H82" s="8" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I82" s="9" t="n">
-        <v>0.06408276714021001</v>
+      <c r="B82" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>1717</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>2183</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>1267</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>510</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>318</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>6061</v>
       </c>
     </row>
     <row r="83">
@@ -3234,29 +4583,29 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B83" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" s="8" t="n">
-        <v>0.05496828752642706</v>
-      </c>
-      <c r="D83" s="8" t="n">
-        <v>0.08449477351916376</v>
-      </c>
-      <c r="E83" s="8" t="n">
-        <v>0.1114285714285714</v>
-      </c>
-      <c r="F83" s="8" t="n">
-        <v>0.09454545454545454</v>
-      </c>
-      <c r="G83" s="8" t="n">
-        <v>0.1381957773512476</v>
-      </c>
-      <c r="H83" s="8" t="n">
-        <v>0.03333333333333333</v>
-      </c>
-      <c r="I83" s="9" t="n">
-        <v>0.0964842717420037</v>
+      <c r="B83" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>447</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>1051</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>933</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>498</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>449</v>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>3418</v>
       </c>
     </row>
     <row r="84">
@@ -3265,29 +4614,29 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B84" s="8" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="C84" s="8" t="n">
-        <v>0.09677419354838709</v>
-      </c>
-      <c r="D84" s="8" t="n">
-        <v>0.1164021164021164</v>
-      </c>
-      <c r="E84" s="8" t="n">
-        <v>0.1104868913857678</v>
-      </c>
-      <c r="F84" s="8" t="n">
-        <v>0.1240694789081886</v>
-      </c>
-      <c r="G84" s="8" t="n">
-        <v>0.1602787456445993</v>
-      </c>
-      <c r="H84" s="8" t="n">
-        <v>0.1176470588235294</v>
-      </c>
-      <c r="I84" s="9" t="n">
-        <v>0.1277971158627549</v>
+      <c r="B84" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>334</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>475</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>353</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>482</v>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>1754</v>
       </c>
     </row>
     <row r="85">
@@ -3296,29 +4645,29 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B85" s="8" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="C85" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="8" t="n">
-        <v>0.2105263157894737</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>0.1583333333333333</v>
-      </c>
-      <c r="F85" s="8" t="n">
-        <v>0.1071428571428571</v>
-      </c>
-      <c r="G85" s="8" t="n">
-        <v>0.1906077348066298</v>
-      </c>
-      <c r="H85" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="9" t="n">
-        <v>0.1688125894134478</v>
+      <c r="B85" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>125</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>293</v>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>581</v>
       </c>
     </row>
     <row r="86">
@@ -3327,28 +4676,289 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B86" s="9" t="n">
+      <c r="B86" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>7249</v>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>5930</v>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>3703</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>1675</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="I86" s="7" t="n">
+        <v>20563</v>
+      </c>
+    </row>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>auto bin - duedate_1m_5_bad_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>primary_model_score_bin</t>
+        </is>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E90" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G90" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H90" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I90" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="8" t="n"/>
+      <c r="D91" s="8" t="n"/>
+      <c r="E91" s="8" t="n"/>
+      <c r="F91" s="8" t="n"/>
+      <c r="G91" s="8" t="n"/>
+      <c r="H91" s="8" t="n"/>
+      <c r="I91" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="8" t="n">
+        <v>0.02933177933177933</v>
+      </c>
+      <c r="D92" s="8" t="n">
+        <v>0.05505709624796085</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>0.0748502994011976</v>
+      </c>
+      <c r="F92" s="8" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="G92" s="8" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H92" s="8" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="I92" s="9" t="n">
+        <v>0.0439344262295082</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="C93" s="8" t="n">
+        <v>0.03539325842696629</v>
+      </c>
+      <c r="D93" s="8" t="n">
+        <v>0.057426597582038</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>0.08387563268257411</v>
+      </c>
+      <c r="F93" s="8" t="n">
+        <v>0.0989399293286219</v>
+      </c>
+      <c r="G93" s="8" t="n">
+        <v>0.1166666666666667</v>
+      </c>
+      <c r="H93" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I93" s="9" t="n">
+        <v>0.06408276714021001</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="8" t="n">
+        <v>0.05496828752642706</v>
+      </c>
+      <c r="D94" s="8" t="n">
+        <v>0.08449477351916376</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>0.1114285714285714</v>
+      </c>
+      <c r="F94" s="8" t="n">
+        <v>0.09454545454545454</v>
+      </c>
+      <c r="G94" s="8" t="n">
+        <v>0.1381957773512476</v>
+      </c>
+      <c r="H94" s="8" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="I94" s="9" t="n">
+        <v>0.0964842717420037</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="C95" s="8" t="n">
+        <v>0.09677419354838709</v>
+      </c>
+      <c r="D95" s="8" t="n">
+        <v>0.1164021164021164</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>0.1104868913857678</v>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>0.1240694789081886</v>
+      </c>
+      <c r="G95" s="8" t="n">
+        <v>0.1602787456445993</v>
+      </c>
+      <c r="H95" s="8" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="I95" s="9" t="n">
+        <v>0.1277971158627549</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="C96" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="8" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>0.1583333333333333</v>
+      </c>
+      <c r="F96" s="8" t="n">
+        <v>0.1071428571428571</v>
+      </c>
+      <c r="G96" s="8" t="n">
+        <v>0.1906077348066298</v>
+      </c>
+      <c r="H96" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="9" t="n">
+        <v>0.1688125894134478</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="n">
         <v>0.06944444444444445</v>
       </c>
-      <c r="C86" s="9" t="n">
+      <c r="C97" s="9" t="n">
         <v>0.03320885569485196</v>
       </c>
-      <c r="D86" s="9" t="n">
+      <c r="D97" s="9" t="n">
         <v>0.06628877342150842</v>
       </c>
-      <c r="E86" s="9" t="n">
+      <c r="E97" s="9" t="n">
         <v>0.09439960870628515</v>
       </c>
-      <c r="F86" s="9" t="n">
+      <c r="F97" s="9" t="n">
         <v>0.09720101781170483</v>
       </c>
-      <c r="G86" s="9" t="n">
+      <c r="G97" s="9" t="n">
         <v>0.1493143727780599</v>
       </c>
-      <c r="H86" s="9" t="n">
+      <c r="H97" s="9" t="n">
         <v>0.0625</v>
       </c>
-      <c r="I86" s="10" t="n">
+      <c r="I97" s="10" t="n">
         <v>0.0703887884267631</v>
       </c>
     </row>
@@ -3358,6 +4968,1892 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>manual bin - 全量申请样本交叉分布</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>primary_model_score_manual_bin</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>3075</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>2885</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>6171</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>12601</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>10851</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>8471</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>6589</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>4589</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>317</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>43498</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>3395</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>6628</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>8649</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>11138</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>13644</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>339</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>43904</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>139</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>657</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>2154</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>5190</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>12888</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>42581</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>559</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>64168</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>3405</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>16678</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>19660</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>22342</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>30660</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>60896</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>4100</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>157741</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>manual bin - duedate_3m_30_valid_cnt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>primary_model_score_manual_bin</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1811</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>1453</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>1095</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>684</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>7074</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>207</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>548</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>852</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>1115</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1252</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>3974</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>173</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>415</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1249</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>2261</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2438</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2478</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2625</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>3185</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>12989</v>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>manual bin - duedate_3m_30_bad_cnt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>primary_model_score_manual_bin</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>136</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>182</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>251</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>352</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>398</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>701</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>manual bin - duedate_3m_30_good_cnt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>primary_model_score_manual_bin</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>1910</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>1679</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>1301</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>959</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>586</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>6436</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>195</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>497</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>741</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>933</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>1001</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>3367</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>146</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>335</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>897</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>2127</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>2248</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>2188</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>2227</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>2484</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>11276</v>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>manual bin - duedate_3m_30_bad_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>primary_model_score_manual_bin</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H38" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="8" t="n"/>
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>0.05911330049261083</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>0.07288790723357261</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>0.1046111493461803</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>0.1242009132420091</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>0.1432748538011696</v>
+      </c>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="9" t="n">
+        <v>0.09018942606728866</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="8" t="n">
+        <v>0.05797101449275362</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>0.09306569343065693</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0.1302816901408451</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>0.1632286995515695</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>0.2004792332268371</v>
+      </c>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="9" t="n">
+        <v>0.1527428283844992</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>0.08860759493670886</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>0.1560693641618497</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>0.1927710843373494</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>0.2818254603682946</v>
+      </c>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="9" t="n">
+        <v>0.2412371134020619</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>0.05926581158779301</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>0.07793273174733388</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>0.1170298627925747</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>0.1516190476190476</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>0.2200941915227629</v>
+      </c>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="10" t="n">
+        <v>0.1318808222341982</v>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>manual bin - duedate_1m_5_valid_cnt</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>primary_model_score_manual_bin</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I47" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>3821</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>3233</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>2605</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>1715</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>847</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>12351</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>454</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>1145</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>1675</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>1816</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>1555</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>6715</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>157</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>426</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>762</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>1611</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>3053</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>4325</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>4535</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>4706</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>4293</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>4013</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>176</v>
+      </c>
+      <c r="I52" s="7" t="n">
+        <v>22120</v>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>manual bin - duedate_1m_5_bad_cnt</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>primary_model_score_manual_bin</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>141</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>136</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>134</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>242</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>199</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>403</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>492</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I61" s="7" t="n">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>manual bin - duedate_1m_5_good_cnt</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>primary_model_score_manual_bin</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G65" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H65" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I65" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>3720</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>3107</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>2464</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>1579</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>769</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>11762</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>437</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>1083</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>1541</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>1640</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>1383</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>6151</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>146</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>376</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>671</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>1369</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>4203</v>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>4336</v>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>4381</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>3890</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>3521</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="I70" s="7" t="n">
+        <v>20563</v>
+      </c>
+    </row>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>manual bin - duedate_1m_5_bad_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>primary_model_score_manual_bin</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F74" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G74" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H74" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I74" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="8" t="n"/>
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="8" t="n"/>
+      <c r="F75" s="8" t="n"/>
+      <c r="G75" s="8" t="n"/>
+      <c r="H75" s="8" t="n"/>
+      <c r="I75" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="C76" s="8" t="n">
+        <v>0.02643287097618425</v>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>0.03897309000927931</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>0.05412667946257198</v>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>0.0793002915451895</v>
+      </c>
+      <c r="G76" s="8" t="n">
+        <v>0.09208972845336481</v>
+      </c>
+      <c r="H76" s="8" t="n">
+        <v>0.06122448979591837</v>
+      </c>
+      <c r="I76" s="9" t="n">
+        <v>0.04768844627965347</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="8" t="n">
+        <v>0.03744493392070485</v>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>0.05414847161572053</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>0.09691629955947137</v>
+      </c>
+      <c r="G77" s="8" t="n">
+        <v>0.1106109324758842</v>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="I77" s="9" t="n">
+        <v>0.08399106478034252</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C78" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>0.07006369426751592</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>0.1173708920187793</v>
+      </c>
+      <c r="F78" s="8" t="n">
+        <v>0.1194225721784777</v>
+      </c>
+      <c r="G78" s="8" t="n">
+        <v>0.1502172563625078</v>
+      </c>
+      <c r="H78" s="8" t="n">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="I78" s="9" t="n">
+        <v>0.1323288568621029</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="n">
+        <v>0.06944444444444445</v>
+      </c>
+      <c r="C79" s="9" t="n">
+        <v>0.02820809248554913</v>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>0.04388092613009923</v>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>0.06906077348066299</v>
+      </c>
+      <c r="F79" s="9" t="n">
+        <v>0.09387374796179827</v>
+      </c>
+      <c r="G79" s="9" t="n">
+        <v>0.1226015449788188</v>
+      </c>
+      <c r="H79" s="9" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="I79" s="10" t="n">
+        <v>0.0703887884267631</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5010,7 +8506,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6663,7 +10159,1644 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>avg_PTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>primary_model_score_bin</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="n">
+        <v>0.0481506939467949</v>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>0.05789565930741281</v>
+      </c>
+      <c r="D3" s="14" t="n">
+        <v>0.03967809364229422</v>
+      </c>
+      <c r="E3" s="14" t="n">
+        <v>0.03504252743057822</v>
+      </c>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n">
+        <v>0.0861793395228581</v>
+      </c>
+      <c r="I3" s="15" t="n">
+        <v>0.04839407935953031</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>0.03957343713334053</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>0.05104429953261285</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>0.04736675801224482</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>0.04552112037069594</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>0.04867776765083955</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>0.04050307110686641</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>0.0574505619296198</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>0.04924409034467404</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>0.04635323987187542</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>0.05030011065530712</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>0.04548503032941518</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>0.04444795340278093</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0.04370883396210247</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>0.04143227868570769</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>0.04770152669152326</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>0.04626719784661767</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>0.03091320446195365</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>0.04861344561317164</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>0.04318659976829168</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>0.04174387481106429</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>0.04221400396672818</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>0.03859117844741119</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0.04499728627888698</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>0.04271758425937038</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>0.03954854268661055</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>0.04704474176230655</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>0.04229614384373771</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>0.03959861455821418</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>0.03927632533114409</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>0.038112124026008</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0.04151539263470797</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>0.04004625529179589</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>0.05598078633698034</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0.03445107278541797</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>0.03911576804136824</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0.03598375565906878</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>0.03467885737594234</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0.03304623996006704</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0.0308985376146458</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>0.03466012532572495</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>0.04193792693892595</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>0.05066055472132761</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>0.0455235489904727</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.0431086190525217</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0.04251180572340478</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>0.03809913111359703</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>0.0500500976841957</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>0.04598536943533156</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>avg_requested_loan_amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>primary_model_score_bin</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>3450</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>2663.333333333333</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>2321.153846153846</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>2140</v>
+      </c>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>2550.714285714286</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>2546.25</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>2394.211932650073</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>2399.054095826893</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>2474.14517669532</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>2463.725490196078</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>2469.96052631579</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>2606.333333333333</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>2409.541027766266</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>2246.428571428572</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>2122.75</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>2041.364600326264</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>2104.889426399447</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>2173.365724381626</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>2276.319444444444</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>2041.346153846154</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>2101.699176228302</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>1418.181818181818</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>1869.685039370079</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>1816.021986970684</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>1901.889388489209</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>1912.318181818182</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>1970.547024952015</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>2160</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>1882.223737373737</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>1350</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>1613.679245283019</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>1824.259259259259</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>1820.953736654804</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>1823.94540942928</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>1961.543554006969</v>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>1480.882352941177</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>1844.926406926407</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>1100</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>1833.333333333333</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>1638.636363636364</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>1508.587786259542</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>1643.035714285714</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>1728.383977900553</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>2061.111111111111</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>1662.586685159501</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>1959.027777777778</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>2286.160645080635</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>2121.06087085308</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>2087.083410780669</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>2036.068702290076</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>2017.859319451498</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>2256.25</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>2156.224951602495</v>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>avg_total_amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>primary_model_score_bin</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>1745</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>913.4615384615385</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>620</v>
+      </c>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>1583.75</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>1470.503477306003</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>1236.396831530139</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>1182.975167144222</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>1374.428104575163</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>1275.664473684211</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>1597</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>1371.64598010775</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>1372.619047619048</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>1154.684210526316</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>983.9502446982056</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>931.046993780235</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>1035.955830388693</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>1074.861111111111</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>1126.923076923077</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>1031.847160929685</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>718.1818181818181</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>955.8956692913385</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>831.2011400651465</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>786.9784172661871</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>876.2854545454545</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>865.9712092130518</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>1054.166666666667</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>846.9906565656565</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>812.5</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>819.811320754717</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>752.0148148148148</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>684.2918149466192</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>758.7468982630273</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>793.0156794425087</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>851.4705882352941</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>750.9518999518999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>957.1428571428571</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>666.6666666666666</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>667.4242424242424</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>614.8854961832061</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>654.1071428571429</v>
+      </c>
+      <c r="G30" s="11" t="n">
+        <v>673.4143646408839</v>
+      </c>
+      <c r="H30" s="11" t="n">
+        <v>702.7777777777778</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>661.5478502080443</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n">
+        <v>1207.638888888889</v>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>1354.09438679835</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>1035.788951421801</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>912.9047397769517</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>959.9150127226463</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>879.1208735398679</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>1257.065217391304</v>
+      </c>
+      <c r="I31" s="13" t="n">
+        <v>1105.169369756937</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>avg_gross_surplus</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>primary_model_score_bin</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>1623.548333333333</v>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>2354.435777777778</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>2995.438333333334</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>1305.005</v>
+      </c>
+      <c r="F36" s="11" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="11" t="n">
+        <v>1726.031666666666</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>2403.766857142857</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n">
+        <v>1787.721</v>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>1858.983769826744</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>2136.02619075219</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>2899.829210442534</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>2990.34461328976</v>
+      </c>
+      <c r="G37" s="11" t="n">
+        <v>4197.442565789474</v>
+      </c>
+      <c r="H37" s="11" t="n">
+        <v>3415.649466666667</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>2130.815285433071</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>1168.733015873016</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>1306.221754385965</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>1560.27134584013</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>1878.113578668509</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>2080.138038869258</v>
+      </c>
+      <c r="G38" s="11" t="n">
+        <v>2543.819055555555</v>
+      </c>
+      <c r="H38" s="11" t="n">
+        <v>1750.435833333333</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>1652.535461655389</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>1102.047424242424</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>1078.012716535433</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>1342.053341476656</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>1569.090355215827</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>1687.568842424242</v>
+      </c>
+      <c r="G39" s="11" t="n">
+        <v>1887.643541266795</v>
+      </c>
+      <c r="H39" s="11" t="n">
+        <v>1374.555722222222</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>1491.284035353535</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>1459.408888888889</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>1003.215314465409</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>1181.700855967078</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>1350.383674377224</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>1515.709139784946</v>
+      </c>
+      <c r="G40" s="11" t="n">
+        <v>1722.907288037166</v>
+      </c>
+      <c r="H40" s="11" t="n">
+        <v>1654.724117647059</v>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>1437.839383517717</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>517.8704761904762</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>637.0361111111112</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>1174.037878787879</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>1296.914732824427</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>1518.313178571428</v>
+      </c>
+      <c r="G41" s="11" t="n">
+        <v>1620.929719152855</v>
+      </c>
+      <c r="H41" s="11" t="n">
+        <v>1942.647777777777</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>1486.343791030975</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n">
+        <v>1321.970601851852</v>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>1666.760681126807</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>1717.547196386256</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>1959.553087050805</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>1956.21428668363</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>2088.86427458947</v>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>2368.332699275362</v>
+      </c>
+      <c r="I42" s="13" t="n">
+        <v>1800.434664443966</v>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>avg_net_surplus</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>primary_model_score_bin</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H46" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I46" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>1266.871666666667</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>1968.387777777777</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>2710.91</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>1112.362333333333</v>
+      </c>
+      <c r="F47" s="11" t="n"/>
+      <c r="G47" s="11" t="n"/>
+      <c r="H47" s="11" t="n">
+        <v>1408.268333333333</v>
+      </c>
+      <c r="I47" s="12" t="n">
+        <v>2085.845666666667</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>1482.654333333333</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>1475.278543191801</v>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>1785.719741756826</v>
+      </c>
+      <c r="E48" s="11" t="n">
+        <v>2536.787924227952</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>2595.545659041394</v>
+      </c>
+      <c r="G48" s="11" t="n">
+        <v>3802.253256578947</v>
+      </c>
+      <c r="H48" s="11" t="n">
+        <v>2992.397488888889</v>
+      </c>
+      <c r="I48" s="12" t="n">
+        <v>1757.62991849703</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>908.3471428571427</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>1029.126868421053</v>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>1303.248524333877</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>1614.482173462336</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>1804.57386925795</v>
+      </c>
+      <c r="G49" s="11" t="n">
+        <v>2253.811023148148</v>
+      </c>
+      <c r="H49" s="11" t="n">
+        <v>1477.272083333333</v>
+      </c>
+      <c r="I49" s="12" t="n">
+        <v>1385.071543591252</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>944.2727272727271</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>846.5747998687664</v>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>1129.92529451683</v>
+      </c>
+      <c r="E50" s="11" t="n">
+        <v>1354.361393884892</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>1460.425475757576</v>
+      </c>
+      <c r="G50" s="11" t="n">
+        <v>1659.045486244402</v>
+      </c>
+      <c r="H50" s="11" t="n">
+        <v>1153.121666666666</v>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>1271.776638888889</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>1257.300416666667</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>810.7086163522014</v>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>995.2937489711933</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>1169.75534400949</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>1327.474892473118</v>
+      </c>
+      <c r="G51" s="11" t="n">
+        <v>1522.506588269454</v>
+      </c>
+      <c r="H51" s="11" t="n">
+        <v>1456.053529411764</v>
+      </c>
+      <c r="I51" s="12" t="n">
+        <v>1248.274777938111</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>317.0947619047619</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>493.5197222222222</v>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>1013.826338383838</v>
+      </c>
+      <c r="E52" s="11" t="n">
+        <v>1143.15665394402</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>1359.908642857143</v>
+      </c>
+      <c r="G52" s="11" t="n">
+        <v>1462.628862799263</v>
+      </c>
+      <c r="H52" s="11" t="n">
+        <v>1783.571111111111</v>
+      </c>
+      <c r="I52" s="12" t="n">
+        <v>1328.374257975034</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="n">
+        <v>1079.021064814815</v>
+      </c>
+      <c r="C53" s="12" t="n">
+        <v>1320.758226861691</v>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>1438.06348810229</v>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>1698.638561415737</v>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>1701.892816793893</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>1857.322291349247</v>
+      </c>
+      <c r="H53" s="12" t="n">
+        <v>2054.646349637681</v>
+      </c>
+      <c r="I53" s="13" t="n">
+        <v>1507.529426471643</v>
+      </c>
+    </row>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>avg_total_income</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>primary_model_score_bin</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H57" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I57" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="n">
+        <v>7407.508333333333</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>7453.876444444445</v>
+      </c>
+      <c r="D58" s="11" t="n">
+        <v>8066.221666666666</v>
+      </c>
+      <c r="E58" s="11" t="n">
+        <v>5845.151</v>
+      </c>
+      <c r="F58" s="11" t="n"/>
+      <c r="G58" s="11" t="n"/>
+      <c r="H58" s="11" t="n">
+        <v>3687.233333333333</v>
+      </c>
+      <c r="I58" s="12" t="n">
+        <v>7342.557857142857</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>8053.924666666666</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>7981.083088396778</v>
+      </c>
+      <c r="D59" s="11" t="n">
+        <v>7894.584024987119</v>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>8686.773664438078</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>8787.170010893247</v>
+      </c>
+      <c r="G59" s="11" t="n">
+        <v>10599.53317982456</v>
+      </c>
+      <c r="H59" s="11" t="n">
+        <v>9012.360066666664</v>
+      </c>
+      <c r="I59" s="12" t="n">
+        <v>8109.395155753556</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>6016.514523809524</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>5822.459442982456</v>
+      </c>
+      <c r="D60" s="11" t="n">
+        <v>6064.638862833061</v>
+      </c>
+      <c r="E60" s="11" t="n">
+        <v>6389.749773093758</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>6745.209552414605</v>
+      </c>
+      <c r="G60" s="11" t="n">
+        <v>7543.537263888889</v>
+      </c>
+      <c r="H60" s="11" t="n">
+        <v>5964.55875</v>
+      </c>
+      <c r="I60" s="12" t="n">
+        <v>6200.220835049524</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>5624.32787878788</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>4976.803051181102</v>
+      </c>
+      <c r="D61" s="11" t="n">
+        <v>5194.10924267101</v>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v>5464.739330035971</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>5749.877348484848</v>
+      </c>
+      <c r="G61" s="11" t="n">
+        <v>6369.221122840691</v>
+      </c>
+      <c r="H61" s="11" t="n">
+        <v>5324.425888888888</v>
+      </c>
+      <c r="I61" s="12" t="n">
+        <v>5476.20438510101</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>4880.051944444444</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>4343.915455974842</v>
+      </c>
+      <c r="D62" s="11" t="n">
+        <v>4600.455246913581</v>
+      </c>
+      <c r="E62" s="11" t="n">
+        <v>4870.279789442467</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>5056.16564516129</v>
+      </c>
+      <c r="G62" s="11" t="n">
+        <v>5580.595383275261</v>
+      </c>
+      <c r="H62" s="11" t="n">
+        <v>5184.736470588235</v>
+      </c>
+      <c r="I62" s="12" t="n">
+        <v>5025.653825557159</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>3580.299047619047</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>4215.881944444444</v>
+      </c>
+      <c r="D63" s="11" t="n">
+        <v>4191.237095959596</v>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>4560.19209923664</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>4901.328869047618</v>
+      </c>
+      <c r="G63" s="11" t="n">
+        <v>5168.099364640883</v>
+      </c>
+      <c r="H63" s="11" t="n">
+        <v>5376.402777777777</v>
+      </c>
+      <c r="I63" s="12" t="n">
+        <v>4895.686317614424</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="n">
+        <v>6115.599027777778</v>
+      </c>
+      <c r="C64" s="12" t="n">
+        <v>7225.538862774513</v>
+      </c>
+      <c r="D64" s="12" t="n">
+        <v>6505.437056180885</v>
+      </c>
+      <c r="E64" s="12" t="n">
+        <v>6454.813718633828</v>
+      </c>
+      <c r="F64" s="12" t="n">
+        <v>6306.827464800678</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>6459.766573556797</v>
+      </c>
+      <c r="H64" s="12" t="n">
+        <v>6989.305516304347</v>
+      </c>
+      <c r="I64" s="13" t="n">
+        <v>6725.827761167277</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10223,7 +15356,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15127,7 +20260,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16019,1339 +21152,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AJ8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="37" customWidth="1" min="12" max="12"/>
-    <col width="39" customWidth="1" min="13" max="13"/>
-    <col width="35" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
-    <col width="38" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="27" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="27" customWidth="1" min="25" max="25"/>
-    <col width="26" customWidth="1" min="26" max="26"/>
-    <col width="31" customWidth="1" min="27" max="27"/>
-    <col width="33" customWidth="1" min="28" max="28"/>
-    <col width="17" customWidth="1" min="29" max="29"/>
-    <col width="17" customWidth="1" min="30" max="30"/>
-    <col width="22" customWidth="1" min="31" max="31"/>
-    <col width="22" customWidth="1" min="32" max="32"/>
-    <col width="22" customWidth="1" min="33" max="33"/>
-    <col width="21" customWidth="1" min="34" max="34"/>
-    <col width="23" customWidth="1" min="35" max="35"/>
-    <col width="20" customWidth="1" min="36" max="36"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>comparison_model_score_bin</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>sample_cnt</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sample_pct</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_valid_cnt</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_bad_cnt</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_good_cnt</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_bad_rate</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_valid_cnt</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_bad_cnt</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_good_cnt</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_bad_rate</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_amount_overdue_amount</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_amount_principal_amount</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_amount_overdue_rate</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_amount_overdue_amount</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_amount_principal_amount</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_amount_overdue_rate</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>avg_PTI</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>avg_requested_loan_amount</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>avg_total_amount</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>avg_gross_surplus</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>avg_net_surplus</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>avg_total_income</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>apply_cnt</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>completed_application_cnt</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>approved_application_cnt</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>auto_approved_application_cnt</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>manual_approved_application_cnt</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>deal_sample_cnt</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>completion_rate</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>approval_rate</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>auto_approval_rate</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>manual_approval_rate</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>auto_approval_share</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>manual_approval_share</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>deal_rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="B2" s="4" t="n">
-        <v>3405</v>
-      </c>
-      <c r="C2" s="8" t="n">
-        <v>0.02158601758578936</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="K2" s="8" t="n">
-        <v>0.06944444444444445</v>
-      </c>
-      <c r="L2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="11" t="n">
-        <v>86950</v>
-      </c>
-      <c r="N2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="11" t="n">
-        <v>10366.75</v>
-      </c>
-      <c r="P2" s="11" t="n">
-        <v>86950</v>
-      </c>
-      <c r="Q2" s="8" t="n">
-        <v>0.1192265669925244</v>
-      </c>
-      <c r="R2" s="14" t="n">
-        <v>0.04193792693892595</v>
-      </c>
-      <c r="S2" s="11" t="n">
-        <v>1834.001762114538</v>
-      </c>
-      <c r="T2" s="11" t="n">
-        <v>1207.638888888889</v>
-      </c>
-      <c r="U2" s="11" t="n">
-        <v>-487.8318722466961</v>
-      </c>
-      <c r="V2" s="11" t="n">
-        <v>-905.5644292706803</v>
-      </c>
-      <c r="W2" s="11" t="n">
-        <v>1117.251026921194</v>
-      </c>
-      <c r="X2" s="4" t="n">
-        <v>3405</v>
-      </c>
-      <c r="Y2" s="4" t="n">
-        <v>3405</v>
-      </c>
-      <c r="Z2" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="AA2" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB2" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="AC2" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="AD2" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="8" t="n">
-        <v>0.02320117474302496</v>
-      </c>
-      <c r="AF2" s="8" t="n">
-        <v>0.000881057268722467</v>
-      </c>
-      <c r="AG2" s="8" t="n">
-        <v>0.0223201174743025</v>
-      </c>
-      <c r="AH2" s="8" t="n">
-        <v>0.0379746835443038</v>
-      </c>
-      <c r="AI2" s="8" t="n">
-        <v>0.9620253164556962</v>
-      </c>
-      <c r="AJ2" s="8" t="n">
-        <v>0.9113924050632911</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>30048</v>
-      </c>
-      <c r="C3" s="8" t="n">
-        <v>0.1904894732504549</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>3961</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>268</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>3693</v>
-      </c>
-      <c r="G3" s="8" t="n">
-        <v>0.06765968189851047</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>7498</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>249</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>7249</v>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>0.03320885569485196</v>
-      </c>
-      <c r="L3" s="11" t="n">
-        <v>327244.2500000001</v>
-      </c>
-      <c r="M3" s="11" t="n">
-        <v>10817326</v>
-      </c>
-      <c r="N3" s="8" t="n">
-        <v>0.03025186168929364</v>
-      </c>
-      <c r="O3" s="11" t="n">
-        <v>488405.03</v>
-      </c>
-      <c r="P3" s="11" t="n">
-        <v>10817326</v>
-      </c>
-      <c r="Q3" s="8" t="n">
-        <v>0.04515025524792356</v>
-      </c>
-      <c r="R3" s="14" t="n">
-        <v>0.05066055472132761</v>
-      </c>
-      <c r="S3" s="11" t="n">
-        <v>2308.134451544196</v>
-      </c>
-      <c r="T3" s="11" t="n">
-        <v>1354.09438679835</v>
-      </c>
-      <c r="U3" s="11" t="n">
-        <v>177.0520408457579</v>
-      </c>
-      <c r="V3" s="11" t="n">
-        <v>-144.5270471689741</v>
-      </c>
-      <c r="W3" s="11" t="n">
-        <v>6252.549996283725</v>
-      </c>
-      <c r="X3" s="4" t="n">
-        <v>30048</v>
-      </c>
-      <c r="Y3" s="4" t="n">
-        <v>30048</v>
-      </c>
-      <c r="Z3" s="4" t="n">
-        <v>9480</v>
-      </c>
-      <c r="AA3" s="4" t="n">
-        <v>2887</v>
-      </c>
-      <c r="AB3" s="4" t="n">
-        <v>6593</v>
-      </c>
-      <c r="AC3" s="4" t="n">
-        <v>7999</v>
-      </c>
-      <c r="AD3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE3" s="8" t="n">
-        <v>0.3154952076677316</v>
-      </c>
-      <c r="AF3" s="8" t="n">
-        <v>0.09607960596379127</v>
-      </c>
-      <c r="AG3" s="8" t="n">
-        <v>0.2194156017039404</v>
-      </c>
-      <c r="AH3" s="8" t="n">
-        <v>0.3045358649789029</v>
-      </c>
-      <c r="AI3" s="8" t="n">
-        <v>0.6954641350210971</v>
-      </c>
-      <c r="AJ3" s="8" t="n">
-        <v>0.8437763713080169</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>30047</v>
-      </c>
-      <c r="C4" s="8" t="n">
-        <v>0.1904831337445559</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>3365</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>370</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>2995</v>
-      </c>
-      <c r="G4" s="8" t="n">
-        <v>0.1099554234769688</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>6351</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>421</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>5930</v>
-      </c>
-      <c r="K4" s="8" t="n">
-        <v>0.06628877342150842</v>
-      </c>
-      <c r="L4" s="11" t="n">
-        <v>396241.16</v>
-      </c>
-      <c r="M4" s="11" t="n">
-        <v>6982597</v>
-      </c>
-      <c r="N4" s="8" t="n">
-        <v>0.05674696105188371</v>
-      </c>
-      <c r="O4" s="11" t="n">
-        <v>558630.89</v>
-      </c>
-      <c r="P4" s="11" t="n">
-        <v>6982597</v>
-      </c>
-      <c r="Q4" s="8" t="n">
-        <v>0.08000331252111499</v>
-      </c>
-      <c r="R4" s="14" t="n">
-        <v>0.0455235489904727</v>
-      </c>
-      <c r="S4" s="11" t="n">
-        <v>2104.14214397444</v>
-      </c>
-      <c r="T4" s="11" t="n">
-        <v>1035.788951421801</v>
-      </c>
-      <c r="U4" s="11" t="n">
-        <v>563.000201573091</v>
-      </c>
-      <c r="V4" s="11" t="n">
-        <v>270.4526173994076</v>
-      </c>
-      <c r="W4" s="11" t="n">
-        <v>5550.268271374846</v>
-      </c>
-      <c r="X4" s="4" t="n">
-        <v>30047</v>
-      </c>
-      <c r="Y4" s="4" t="n">
-        <v>30047</v>
-      </c>
-      <c r="Z4" s="4" t="n">
-        <v>8002</v>
-      </c>
-      <c r="AA4" s="4" t="n">
-        <v>2669</v>
-      </c>
-      <c r="AB4" s="4" t="n">
-        <v>5333</v>
-      </c>
-      <c r="AC4" s="4" t="n">
-        <v>6752</v>
-      </c>
-      <c r="AD4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="8" t="n">
-        <v>0.2663161047691949</v>
-      </c>
-      <c r="AF4" s="8" t="n">
-        <v>0.08882750357772823</v>
-      </c>
-      <c r="AG4" s="8" t="n">
-        <v>0.1774886011914667</v>
-      </c>
-      <c r="AH4" s="8" t="n">
-        <v>0.3335416145963509</v>
-      </c>
-      <c r="AI4" s="8" t="n">
-        <v>0.6664583854036491</v>
-      </c>
-      <c r="AJ4" s="8" t="n">
-        <v>0.8437890527368158</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>30047</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>0.1904831337445559</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>2533</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>382</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>2151</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>0.1508093170153968</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>4089</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>386</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>3703</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>0.09439960870628515</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>368557.58</v>
-      </c>
-      <c r="M5" s="11" t="n">
-        <v>3927842</v>
-      </c>
-      <c r="N5" s="8" t="n">
-        <v>0.09383207878524644</v>
-      </c>
-      <c r="O5" s="11" t="n">
-        <v>469589.6799999999</v>
-      </c>
-      <c r="P5" s="11" t="n">
-        <v>3927842</v>
-      </c>
-      <c r="Q5" s="8" t="n">
-        <v>0.1195541164843189</v>
-      </c>
-      <c r="R5" s="14" t="n">
-        <v>0.0431086190525217</v>
-      </c>
-      <c r="S5" s="11" t="n">
-        <v>1960.415449129697</v>
-      </c>
-      <c r="T5" s="11" t="n">
-        <v>912.9047397769517</v>
-      </c>
-      <c r="U5" s="11" t="n">
-        <v>915.48970107942</v>
-      </c>
-      <c r="V5" s="11" t="n">
-        <v>627.7629505996161</v>
-      </c>
-      <c r="W5" s="11" t="n">
-        <v>5243.57630906025</v>
-      </c>
-      <c r="X5" s="4" t="n">
-        <v>30047</v>
-      </c>
-      <c r="Y5" s="4" t="n">
-        <v>30047</v>
-      </c>
-      <c r="Z5" s="4" t="n">
-        <v>5075</v>
-      </c>
-      <c r="AA5" s="4" t="n">
-        <v>1691</v>
-      </c>
-      <c r="AB5" s="4" t="n">
-        <v>3384</v>
-      </c>
-      <c r="AC5" s="4" t="n">
-        <v>4304</v>
-      </c>
-      <c r="AD5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE5" s="8" t="n">
-        <v>0.1689020534495956</v>
-      </c>
-      <c r="AF5" s="8" t="n">
-        <v>0.05627849702133324</v>
-      </c>
-      <c r="AG5" s="8" t="n">
-        <v>0.1126235564282624</v>
-      </c>
-      <c r="AH5" s="8" t="n">
-        <v>0.3332019704433498</v>
-      </c>
-      <c r="AI5" s="8" t="n">
-        <v>0.6667980295566502</v>
-      </c>
-      <c r="AJ5" s="8" t="n">
-        <v>0.8480788177339902</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>30047</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>0.1904831337445559</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1552</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>277</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>1275</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>0.178479381443299</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>1965</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>191</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>1774</v>
-      </c>
-      <c r="K6" s="8" t="n">
-        <v>0.09720101781170483</v>
-      </c>
-      <c r="L6" s="11" t="n">
-        <v>244019.8</v>
-      </c>
-      <c r="M6" s="11" t="n">
-        <v>1886233</v>
-      </c>
-      <c r="N6" s="8" t="n">
-        <v>0.1293688531586501</v>
-      </c>
-      <c r="O6" s="11" t="n">
-        <v>286950.21</v>
-      </c>
-      <c r="P6" s="11" t="n">
-        <v>1886233</v>
-      </c>
-      <c r="Q6" s="8" t="n">
-        <v>0.1521287189864667</v>
-      </c>
-      <c r="R6" s="14" t="n">
-        <v>0.04251180572340477</v>
-      </c>
-      <c r="S6" s="11" t="n">
-        <v>1857.072053782407</v>
-      </c>
-      <c r="T6" s="11" t="n">
-        <v>959.9150127226463</v>
-      </c>
-      <c r="U6" s="11" t="n">
-        <v>736.9061559112944</v>
-      </c>
-      <c r="V6" s="11" t="n">
-        <v>441.8838940104946</v>
-      </c>
-      <c r="W6" s="11" t="n">
-        <v>4643.697768606961</v>
-      </c>
-      <c r="X6" s="4" t="n">
-        <v>30047</v>
-      </c>
-      <c r="Y6" s="4" t="n">
-        <v>30047</v>
-      </c>
-      <c r="Z6" s="4" t="n">
-        <v>2262</v>
-      </c>
-      <c r="AA6" s="4" t="n">
-        <v>597</v>
-      </c>
-      <c r="AB6" s="4" t="n">
-        <v>1665</v>
-      </c>
-      <c r="AC6" s="4" t="n">
-        <v>1965</v>
-      </c>
-      <c r="AD6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE6" s="8" t="n">
-        <v>0.07528205810896263</v>
-      </c>
-      <c r="AF6" s="8" t="n">
-        <v>0.01986887210037608</v>
-      </c>
-      <c r="AG6" s="8" t="n">
-        <v>0.05541318600858654</v>
-      </c>
-      <c r="AH6" s="8" t="n">
-        <v>0.2639257294429708</v>
-      </c>
-      <c r="AI6" s="8" t="n">
-        <v>0.7360742705570292</v>
-      </c>
-      <c r="AJ6" s="8" t="n">
-        <v>0.8687002652519894</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>30047</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>0.1904831337445559</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1576</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>416</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>1160</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>0.2639593908629442</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>1969</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>294</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>1675</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>0.1493143727780599</v>
-      </c>
-      <c r="L7" s="11" t="n">
-        <v>341067.65</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>1730989</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>0.1970362896586864</v>
-      </c>
-      <c r="O7" s="11" t="n">
-        <v>386468.5700000001</v>
-      </c>
-      <c r="P7" s="11" t="n">
-        <v>1730989</v>
-      </c>
-      <c r="Q7" s="8" t="n">
-        <v>0.2232646019125483</v>
-      </c>
-      <c r="R7" s="14" t="n">
-        <v>0.03809913111359703</v>
-      </c>
-      <c r="S7" s="11" t="n">
-        <v>1722.414716943455</v>
-      </c>
-      <c r="T7" s="11" t="n">
-        <v>879.1208735398679</v>
-      </c>
-      <c r="U7" s="11" t="n">
-        <v>1368.75337016452</v>
-      </c>
-      <c r="V7" s="11" t="n">
-        <v>1104.727413330227</v>
-      </c>
-      <c r="W7" s="11" t="n">
-        <v>5644.138230383509</v>
-      </c>
-      <c r="X7" s="4" t="n">
-        <v>30047</v>
-      </c>
-      <c r="Y7" s="4" t="n">
-        <v>30047</v>
-      </c>
-      <c r="Z7" s="4" t="n">
-        <v>2207</v>
-      </c>
-      <c r="AA7" s="4" t="n">
-        <v>297</v>
-      </c>
-      <c r="AB7" s="4" t="n">
-        <v>1910</v>
-      </c>
-      <c r="AC7" s="4" t="n">
-        <v>1969</v>
-      </c>
-      <c r="AD7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="8" t="n">
-        <v>0.07345159250507538</v>
-      </c>
-      <c r="AF7" s="8" t="n">
-        <v>0.009884514260991115</v>
-      </c>
-      <c r="AG7" s="8" t="n">
-        <v>0.06356707824408427</v>
-      </c>
-      <c r="AH7" s="8" t="n">
-        <v>0.1345718169460806</v>
-      </c>
-      <c r="AI7" s="8" t="n">
-        <v>0.8654281830539193</v>
-      </c>
-      <c r="AJ7" s="8" t="n">
-        <v>0.8921613049388309</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n"/>
-      <c r="B8" s="4" t="n">
-        <v>4100</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>0.02599197418553198</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="4" t="n">
-        <v>176</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>165</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="L8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="11" t="n">
-        <v>231300</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="11" t="n">
-        <v>10504.48</v>
-      </c>
-      <c r="P8" s="11" t="n">
-        <v>231300</v>
-      </c>
-      <c r="Q8" s="8" t="n">
-        <v>0.04541495892779939</v>
-      </c>
-      <c r="R8" s="14" t="n">
-        <v>0.0500500976841957</v>
-      </c>
-      <c r="S8" s="11" t="n">
-        <v>1876.664878048781</v>
-      </c>
-      <c r="T8" s="11" t="n">
-        <v>1257.065217391304</v>
-      </c>
-      <c r="U8" s="11" t="n">
-        <v>-563.9332463414636</v>
-      </c>
-      <c r="V8" s="11" t="n">
-        <v>-958.8505967479674</v>
-      </c>
-      <c r="W8" s="11" t="n">
-        <v>1581.861180487805</v>
-      </c>
-      <c r="X8" s="4" t="n">
-        <v>4100</v>
-      </c>
-      <c r="Y8" s="4" t="n">
-        <v>4100</v>
-      </c>
-      <c r="Z8" s="4" t="n">
-        <v>208</v>
-      </c>
-      <c r="AA8" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="AB8" s="4" t="n">
-        <v>163</v>
-      </c>
-      <c r="AC8" s="4" t="n">
-        <v>184</v>
-      </c>
-      <c r="AD8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE8" s="8" t="n">
-        <v>0.05073170731707317</v>
-      </c>
-      <c r="AF8" s="8" t="n">
-        <v>0.01097560975609756</v>
-      </c>
-      <c r="AG8" s="8" t="n">
-        <v>0.03975609756097561</v>
-      </c>
-      <c r="AH8" s="8" t="n">
-        <v>0.2163461538461539</v>
-      </c>
-      <c r="AI8" s="8" t="n">
-        <v>0.7836538461538461</v>
-      </c>
-      <c r="AJ8" s="8" t="n">
-        <v>0.8846153846153846</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AI2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="37" customWidth="1" min="11" max="11"/>
-    <col width="39" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
-    <col width="36" customWidth="1" min="14" max="14"/>
-    <col width="38" customWidth="1" min="15" max="15"/>
-    <col width="34" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="27" customWidth="1" min="18" max="18"/>
-    <col width="19" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="19" customWidth="1" min="21" max="21"/>
-    <col width="19" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
-    <col width="27" customWidth="1" min="24" max="24"/>
-    <col width="26" customWidth="1" min="25" max="25"/>
-    <col width="31" customWidth="1" min="26" max="26"/>
-    <col width="33" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
-    <col width="17" customWidth="1" min="29" max="29"/>
-    <col width="21" customWidth="1" min="30" max="30"/>
-    <col width="22" customWidth="1" min="31" max="31"/>
-    <col width="22" customWidth="1" min="32" max="32"/>
-    <col width="21" customWidth="1" min="33" max="33"/>
-    <col width="23" customWidth="1" min="34" max="34"/>
-    <col width="20" customWidth="1" min="35" max="35"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>sample_cnt</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>sample_pct</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_valid_cnt</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_bad_cnt</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_good_cnt</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_bad_rate</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_valid_cnt</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_bad_cnt</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_good_cnt</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_bad_rate</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_amount_overdue_amount</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_amount_principal_amount</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_amount_overdue_rate</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_amount_overdue_amount</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_amount_principal_amount</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_amount_overdue_rate</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>avg_PTI</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>avg_requested_loan_amount</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>avg_total_amount</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>avg_gross_surplus</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>avg_net_surplus</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>avg_total_income</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>apply_cnt</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>completed_application_cnt</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>approved_application_cnt</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>auto_approved_application_cnt</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>manual_approved_application_cnt</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>deal_sample_cnt</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>completion_rate</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>approval_rate</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>auto_approval_rate</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>manual_approval_rate</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>auto_approval_share</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>manual_approval_share</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>deal_rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n">
-        <v>157741</v>
-      </c>
-      <c r="B2" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>12989</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>1713</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>11276</v>
-      </c>
-      <c r="F2" s="8" t="n">
-        <v>0.1318808222341982</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>22120</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>1557</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>20563</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>0.0703887884267631</v>
-      </c>
-      <c r="K2" s="11" t="n">
-        <v>1677130.44</v>
-      </c>
-      <c r="L2" s="11" t="n">
-        <v>25663237</v>
-      </c>
-      <c r="M2" s="8" t="n">
-        <v>0.06535147690059519</v>
-      </c>
-      <c r="N2" s="11" t="n">
-        <v>2210915.61</v>
-      </c>
-      <c r="O2" s="11" t="n">
-        <v>25663237</v>
-      </c>
-      <c r="P2" s="8" t="n">
-        <v>0.08615108101912475</v>
-      </c>
-      <c r="Q2" s="14" t="n">
-        <v>0.04598536943533157</v>
-      </c>
-      <c r="R2" s="11" t="n">
-        <v>1984.103860125142</v>
-      </c>
-      <c r="S2" s="11" t="n">
-        <v>1105.169369756937</v>
-      </c>
-      <c r="T2" s="11" t="n">
-        <v>691.2584792370616</v>
-      </c>
-      <c r="U2" s="11" t="n">
-        <v>393.6974539382066</v>
-      </c>
-      <c r="V2" s="11" t="n">
-        <v>5271.982231918143</v>
-      </c>
-      <c r="W2" s="4" t="n">
-        <v>157741</v>
-      </c>
-      <c r="X2" s="4" t="n">
-        <v>157741</v>
-      </c>
-      <c r="Y2" s="4" t="n">
-        <v>27313</v>
-      </c>
-      <c r="Z2" s="4" t="n">
-        <v>8189</v>
-      </c>
-      <c r="AA2" s="4" t="n">
-        <v>19124</v>
-      </c>
-      <c r="AB2" s="4" t="n">
-        <v>23245</v>
-      </c>
-      <c r="AC2" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD2" s="8" t="n">
-        <v>0.1731509246169353</v>
-      </c>
-      <c r="AE2" s="8" t="n">
-        <v>0.05191421380617595</v>
-      </c>
-      <c r="AF2" s="8" t="n">
-        <v>0.1212367108107594</v>
-      </c>
-      <c r="AG2" s="8" t="n">
-        <v>0.2998205982499176</v>
-      </c>
-      <c r="AH2" s="8" t="n">
-        <v>0.7001794017500824</v>
-      </c>
-      <c r="AI2" s="8" t="n">
-        <v>0.8510599348295683</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>